--- a/data/matches/leagues/England_Premier_League_2025-2026.xlsx
+++ b/data/matches/leagues/England_Premier_League_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP120" headerRowCount="1">
-  <autoFilter ref="A1:EP120"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP121" headerRowCount="1">
+  <autoFilter ref="A1:EP121"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP120"/>
+  <dimension ref="A1:EP121"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40.8" customWidth="1" min="1" max="1"/>
@@ -5618,7 +5618,7 @@
         <v>0</v>
       </c>
       <c r="DD10" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="DE10" t="n">
         <v>2.17</v>
@@ -5651,7 +5651,7 @@
         <v>0</v>
       </c>
       <c r="DO10" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP10" t="b">
         <v>1</v>
@@ -6109,7 +6109,7 @@
         <v>1.33</v>
       </c>
       <c r="DE11" t="n">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="DF11" t="n">
         <v>0</v>
@@ -6139,7 +6139,7 @@
         <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP11" t="b">
         <v>1</v>
@@ -9431,7 +9431,7 @@
         <v>0</v>
       </c>
       <c r="DO18" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP18" t="b">
         <v>1</v>
@@ -10391,7 +10391,7 @@
         <v>0</v>
       </c>
       <c r="DO20" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP20" t="b">
         <v>1</v>
@@ -12213,7 +12213,7 @@
         <v>0.17</v>
       </c>
       <c r="DE24" t="n">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="DF24" t="n">
         <v>0</v>
@@ -12243,7 +12243,7 @@
         <v>1.81</v>
       </c>
       <c r="DO24" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP24" t="b">
         <v>1</v>
@@ -12694,7 +12694,7 @@
         <v>100</v>
       </c>
       <c r="DD25" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="DE25" t="n">
         <v>0.5</v>
@@ -12727,7 +12727,7 @@
         <v>3.63</v>
       </c>
       <c r="DO25" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -17479,7 +17479,7 @@
         <v>3.05</v>
       </c>
       <c r="DO35" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP35" t="b">
         <v>0</v>
@@ -20327,7 +20327,7 @@
         <v>2.5</v>
       </c>
       <c r="DO41" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP41" t="b">
         <v>1</v>
@@ -20765,7 +20765,7 @@
         <v>2</v>
       </c>
       <c r="DE42" t="n">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="DF42" t="n">
         <v>3</v>
@@ -20795,7 +20795,7 @@
         <v>2.66</v>
       </c>
       <c r="DO42" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP42" t="b">
         <v>1</v>
@@ -23110,7 +23110,7 @@
         <v>100</v>
       </c>
       <c r="DD47" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="DE47" t="n">
         <v>2.17</v>
@@ -23143,7 +23143,7 @@
         <v>4.15</v>
       </c>
       <c r="DO47" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP47" t="b">
         <v>1</v>
@@ -25499,7 +25499,7 @@
         <v>2.25</v>
       </c>
       <c r="DO52" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP52" t="b">
         <v>1</v>
@@ -29711,7 +29711,7 @@
         <v>3.07</v>
       </c>
       <c r="DO61" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP61" t="b">
         <v>1</v>
@@ -31570,7 +31570,7 @@
         <v>67</v>
       </c>
       <c r="DD65" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="DE65" t="n">
         <v>1.17</v>
@@ -31603,7 +31603,7 @@
         <v>3</v>
       </c>
       <c r="DO65" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP65" t="b">
         <v>1</v>
@@ -32979,7 +32979,7 @@
         <v>2.76</v>
       </c>
       <c r="DO68" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP68" t="b">
         <v>1</v>
@@ -35325,7 +35325,7 @@
         <v>2.5</v>
       </c>
       <c r="DE73" t="n">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="DF73" t="n">
         <v>2</v>
@@ -35355,7 +35355,7 @@
         <v>2.81</v>
       </c>
       <c r="DO73" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP73" t="b">
         <v>1</v>
@@ -38647,7 +38647,7 @@
         <v>2.88</v>
       </c>
       <c r="DO80" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP80" t="b">
         <v>1</v>
@@ -39707,40 +39707,40 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Chelsea</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="F83" s="2" t="n">
         <v>45955.58333333334</v>
       </c>
       <c r="G83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I83" t="n">
         <v>3</v>
       </c>
       <c r="J83" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="K83" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L83" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="O83" t="n">
         <v>0</v>
@@ -39752,87 +39752,87 @@
         <v>7</v>
       </c>
       <c r="R83" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="S83" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="T83" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U83" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="V83" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="W83" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="X83" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="Y83" t="n">
-        <v>68</v>
+        <v>51</v>
       </c>
       <c r="Z83" t="n">
-        <v>32</v>
+        <v>49</v>
       </c>
       <c r="AA83" t="inlineStr"/>
       <c r="AB83" t="inlineStr"/>
       <c r="AC83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE83" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AF83" t="n">
+        <v>4</v>
+      </c>
+      <c r="AG83" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AH83" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="AI83" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AJ83" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AK83" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="AL83" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM83" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="AN83" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AO83" t="n">
+        <v>2.97</v>
+      </c>
+      <c r="AP83" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AQ83" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AR83" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="AS83" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AT83" t="n">
         <v>1.45</v>
-      </c>
-      <c r="AF83" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="AG83" t="n">
-        <v>8</v>
-      </c>
-      <c r="AH83" t="n">
-        <v>1.23</v>
-      </c>
-      <c r="AI83" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AJ83" t="n">
-        <v>2.78</v>
-      </c>
-      <c r="AK83" t="n">
-        <v>1.99</v>
-      </c>
-      <c r="AL83" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AM83" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="AN83" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AO83" t="n">
-        <v>2.54</v>
-      </c>
-      <c r="AP83" t="n">
-        <v>2</v>
-      </c>
-      <c r="AQ83" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AR83" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="AS83" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AT83" t="n">
-        <v>1.5</v>
       </c>
       <c r="AU83" t="n">
         <v>3</v>
@@ -39841,28 +39841,28 @@
         <v>1</v>
       </c>
       <c r="AW83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY83" t="n">
         <v>1</v>
       </c>
       <c r="AZ83" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB83" t="n">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="BC83" t="n">
         <v>0</v>
       </c>
       <c r="BD83" t="n">
-        <v>25</v>
+        <v>63</v>
       </c>
       <c r="BE83" t="n">
         <v>0</v>
@@ -39877,13 +39877,13 @@
         <v>1</v>
       </c>
       <c r="BI83" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="BJ83" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BK83" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BL83" t="n">
         <v>1</v>
@@ -39892,49 +39892,49 @@
         <v>5</v>
       </c>
       <c r="BN83" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="BO83" t="n">
         <v>0</v>
       </c>
       <c r="BP83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR83" t="n">
         <v>1</v>
       </c>
       <c r="BS83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT83" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BU83" t="n">
         <v>1</v>
       </c>
       <c r="BV83" t="n">
-        <v>82</v>
+        <v>48</v>
       </c>
       <c r="BW83" t="n">
-        <v>21</v>
+        <v>42</v>
       </c>
       <c r="BX83" t="n">
-        <v>123</v>
+        <v>109</v>
       </c>
       <c r="BY83" t="n">
         <v>76</v>
       </c>
       <c r="BZ83" t="n">
-        <v>2.09</v>
+        <v>1.97</v>
       </c>
       <c r="CA83" t="n">
-        <v>1.07</v>
+        <v>1.41</v>
       </c>
       <c r="CB83" t="n">
-        <v>3.16</v>
+        <v>3.39</v>
       </c>
       <c r="CC83" t="n">
         <v>0</v>
@@ -39961,13 +39961,13 @@
         <v>1</v>
       </c>
       <c r="CK83" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CL83" t="n">
         <v>0</v>
       </c>
       <c r="CM83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN83" t="n">
         <v>0</v>
@@ -39976,40 +39976,40 @@
         <v>0</v>
       </c>
       <c r="CP83" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ83" t="n">
         <v>1</v>
       </c>
       <c r="CR83" t="n">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="CS83" t="n">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="CT83" t="n">
         <v>1</v>
       </c>
       <c r="CU83" t="n">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="CV83" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="CW83" t="n">
         <v>1</v>
       </c>
       <c r="CX83" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="CY83" t="n">
         <v>8</v>
       </c>
       <c r="CZ83" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="DA83" t="n">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="DB83" t="n">
         <v>13</v>
@@ -40018,37 +40018,37 @@
         <v>63</v>
       </c>
       <c r="DD83" t="n">
-        <v>1.67</v>
+        <v>2</v>
       </c>
       <c r="DE83" t="n">
-        <v>1.17</v>
+        <v>0.17</v>
       </c>
       <c r="DF83" t="n">
-        <v>1.75</v>
+        <v>1.5</v>
       </c>
       <c r="DG83" t="n">
-        <v>1</v>
+        <v>0.25</v>
       </c>
       <c r="DH83" t="n">
-        <v>1.75</v>
+        <v>1.13</v>
       </c>
       <c r="DI83" t="n">
-        <v>1.75</v>
+        <v>1</v>
       </c>
       <c r="DJ83" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="DK83" t="n">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="DL83" t="n">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="DM83" t="n">
-        <v>0.97</v>
+        <v>1.22</v>
       </c>
       <c r="DN83" t="n">
-        <v>2.58</v>
+        <v>2.8</v>
       </c>
       <c r="DO83" t="n">
         <v>12</v>
@@ -40075,14 +40075,14 @@
         <v>1</v>
       </c>
       <c r="DW83" t="n">
-        <v>8.699999999999999</v>
+        <v>6.95</v>
       </c>
       <c r="DX83" t="n">
-        <v>6.41</v>
+        <v>10.01</v>
       </c>
       <c r="DY83" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>72%</t>
         </is>
       </c>
       <c r="DZ83" t="inlineStr">
@@ -40092,80 +40092,76 @@
       </c>
       <c r="EA83" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EB83" t="inlineStr">
         <is>
+          <t>3.09</t>
+        </is>
+      </c>
+      <c r="EC83" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="ED83" t="inlineStr">
+        <is>
+          <t>2.44</t>
+        </is>
+      </c>
+      <c r="EE83" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+      <c r="EF83" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
+      </c>
+      <c r="EG83" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="EH83" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EI83" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="EJ83" t="inlineStr"/>
+      <c r="EK83" t="inlineStr"/>
+      <c r="EL83" t="inlineStr">
+        <is>
+          <t>1.46</t>
+        </is>
+      </c>
+      <c r="EM83" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EN83" t="inlineStr">
+        <is>
+          <t>3.19</t>
+        </is>
+      </c>
+      <c r="EO83" t="inlineStr">
+        <is>
           <t>2.78</t>
         </is>
       </c>
-      <c r="EC83" t="inlineStr">
-        <is>
-          <t>1.79</t>
-        </is>
-      </c>
-      <c r="ED83" t="inlineStr">
-        <is>
-          <t>2.04</t>
-        </is>
-      </c>
-      <c r="EE83" t="inlineStr">
-        <is>
-          <t>4.70</t>
-        </is>
-      </c>
-      <c r="EF83" t="inlineStr">
-        <is>
-          <t>7.85</t>
-        </is>
-      </c>
-      <c r="EG83" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
-      <c r="EH83" t="inlineStr">
-        <is>
-          <t>1.94</t>
-        </is>
-      </c>
-      <c r="EI83" t="inlineStr">
-        <is>
-          <t>1.92</t>
-        </is>
-      </c>
-      <c r="EJ83" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="EK83" t="inlineStr">
-        <is>
-          <t>2.61</t>
-        </is>
-      </c>
-      <c r="EL83" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="EM83" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
-      <c r="EN83" t="inlineStr">
-        <is>
-          <t>3.33</t>
-        </is>
-      </c>
-      <c r="EO83" t="inlineStr">
-        <is>
-          <t>2.56</t>
-        </is>
-      </c>
-      <c r="EP83" t="inlineStr"/>
+      <c r="EP83" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -40183,40 +40179,40 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>Chelsea</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F84" s="2" t="n">
         <v>45955.58333333334</v>
       </c>
       <c r="G84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I84" t="n">
         <v>3</v>
       </c>
       <c r="J84" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="K84" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L84" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="M84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="O84" t="n">
         <v>0</v>
@@ -40228,87 +40224,87 @@
         <v>7</v>
       </c>
       <c r="R84" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="S84" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="T84" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="U84" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="V84" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="W84" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="X84" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="Y84" t="n">
-        <v>51</v>
+        <v>68</v>
       </c>
       <c r="Z84" t="n">
-        <v>49</v>
+        <v>32</v>
       </c>
       <c r="AA84" t="inlineStr"/>
       <c r="AB84" t="inlineStr"/>
       <c r="AC84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AE84" t="n">
-        <v>1.57</v>
+        <v>1.45</v>
       </c>
       <c r="AF84" t="n">
-        <v>4</v>
+        <v>4.75</v>
       </c>
       <c r="AG84" t="n">
-        <v>5.5</v>
+        <v>8</v>
       </c>
       <c r="AH84" t="n">
-        <v>1.26</v>
+        <v>1.23</v>
       </c>
       <c r="AI84" t="n">
-        <v>1.87</v>
+        <v>1.72</v>
       </c>
       <c r="AJ84" t="n">
-        <v>3.25</v>
+        <v>2.78</v>
       </c>
       <c r="AK84" t="n">
-        <v>2.04</v>
+        <v>1.99</v>
       </c>
       <c r="AL84" t="n">
-        <v>1.91</v>
+        <v>1.78</v>
       </c>
       <c r="AM84" t="n">
-        <v>1.32</v>
+        <v>1.44</v>
       </c>
       <c r="AN84" t="n">
-        <v>1.55</v>
+        <v>1.95</v>
       </c>
       <c r="AO84" t="n">
-        <v>2.97</v>
+        <v>2.54</v>
       </c>
       <c r="AP84" t="n">
-        <v>2.3</v>
+        <v>2</v>
       </c>
       <c r="AQ84" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AR84" t="n">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="AS84" t="n">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="AT84" t="n">
-        <v>1.45</v>
+        <v>1.5</v>
       </c>
       <c r="AU84" t="n">
         <v>3</v>
@@ -40317,28 +40313,28 @@
         <v>1</v>
       </c>
       <c r="AW84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY84" t="n">
         <v>1</v>
       </c>
       <c r="AZ84" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB84" t="n">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="BC84" t="n">
         <v>0</v>
       </c>
       <c r="BD84" t="n">
-        <v>63</v>
+        <v>25</v>
       </c>
       <c r="BE84" t="n">
         <v>0</v>
@@ -40353,13 +40349,13 @@
         <v>1</v>
       </c>
       <c r="BI84" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="BJ84" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BK84" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BL84" t="n">
         <v>1</v>
@@ -40368,49 +40364,49 @@
         <v>5</v>
       </c>
       <c r="BN84" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BO84" t="n">
         <v>0</v>
       </c>
       <c r="BP84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR84" t="n">
         <v>1</v>
       </c>
       <c r="BS84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT84" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BU84" t="n">
         <v>1</v>
       </c>
       <c r="BV84" t="n">
-        <v>48</v>
+        <v>82</v>
       </c>
       <c r="BW84" t="n">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="BX84" t="n">
-        <v>109</v>
+        <v>123</v>
       </c>
       <c r="BY84" t="n">
         <v>76</v>
       </c>
       <c r="BZ84" t="n">
-        <v>1.97</v>
+        <v>2.09</v>
       </c>
       <c r="CA84" t="n">
-        <v>1.41</v>
+        <v>1.07</v>
       </c>
       <c r="CB84" t="n">
-        <v>3.39</v>
+        <v>3.16</v>
       </c>
       <c r="CC84" t="n">
         <v>0</v>
@@ -40437,13 +40433,13 @@
         <v>1</v>
       </c>
       <c r="CK84" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CL84" t="n">
         <v>0</v>
       </c>
       <c r="CM84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN84" t="n">
         <v>0</v>
@@ -40452,40 +40448,40 @@
         <v>0</v>
       </c>
       <c r="CP84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CQ84" t="n">
         <v>1</v>
       </c>
       <c r="CR84" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="CS84" t="n">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="CT84" t="n">
         <v>1</v>
       </c>
       <c r="CU84" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="CV84" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="CW84" t="n">
         <v>1</v>
       </c>
       <c r="CX84" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="CY84" t="n">
         <v>8</v>
       </c>
       <c r="CZ84" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="DA84" t="n">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="DB84" t="n">
         <v>13</v>
@@ -40494,37 +40490,37 @@
         <v>63</v>
       </c>
       <c r="DD84" t="n">
-        <v>2</v>
+        <v>1.67</v>
       </c>
       <c r="DE84" t="n">
-        <v>0.17</v>
+        <v>1.17</v>
       </c>
       <c r="DF84" t="n">
-        <v>1.5</v>
+        <v>1.75</v>
       </c>
       <c r="DG84" t="n">
-        <v>0.25</v>
+        <v>1</v>
       </c>
       <c r="DH84" t="n">
-        <v>1.13</v>
+        <v>1.75</v>
       </c>
       <c r="DI84" t="n">
-        <v>1</v>
+        <v>1.75</v>
       </c>
       <c r="DJ84" t="n">
-        <v>50</v>
+        <v>75</v>
       </c>
       <c r="DK84" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="DL84" t="n">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="DM84" t="n">
-        <v>1.22</v>
+        <v>0.97</v>
       </c>
       <c r="DN84" t="n">
-        <v>2.8</v>
+        <v>2.58</v>
       </c>
       <c r="DO84" t="n">
         <v>12</v>
@@ -40551,14 +40547,14 @@
         <v>1</v>
       </c>
       <c r="DW84" t="n">
-        <v>6.95</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="DX84" t="n">
-        <v>10.01</v>
+        <v>6.41</v>
       </c>
       <c r="DY84" t="inlineStr">
         <is>
-          <t>72%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="DZ84" t="inlineStr">
@@ -40568,76 +40564,80 @@
       </c>
       <c r="EA84" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="EB84" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="EC84" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.79</t>
         </is>
       </c>
       <c r="ED84" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="EE84" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>4.70</t>
         </is>
       </c>
       <c r="EF84" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>7.85</t>
         </is>
       </c>
       <c r="EG84" t="inlineStr">
         <is>
-          <t>1.61</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="EH84" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="EI84" t="inlineStr">
         <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="EJ84" t="inlineStr"/>
-      <c r="EK84" t="inlineStr"/>
+          <t>1.92</t>
+        </is>
+      </c>
+      <c r="EJ84" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EK84" t="inlineStr">
+        <is>
+          <t>2.61</t>
+        </is>
+      </c>
       <c r="EL84" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="EM84" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="EN84" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="EO84" t="inlineStr">
         <is>
-          <t>2.78</t>
-        </is>
-      </c>
-      <c r="EP84" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
+          <t>2.56</t>
+        </is>
+      </c>
+      <c r="EP84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -40974,7 +40974,7 @@
         <v>100</v>
       </c>
       <c r="DD85" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="DE85" t="n">
         <v>0.83</v>
@@ -41007,7 +41007,7 @@
         <v>3.35</v>
       </c>
       <c r="DO85" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP85" t="b">
         <v>1</v>
@@ -41583,25 +41583,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="F87" s="2" t="n">
         <v>45956.58333333334</v>
       </c>
       <c r="G87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H87" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="I87" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="J87" t="n">
         <v>4</v>
@@ -41613,7 +41613,7 @@
         <v>7</v>
       </c>
       <c r="M87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N87" t="n">
         <v>0</v>
@@ -41625,128 +41625,128 @@
         <v>0</v>
       </c>
       <c r="Q87" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="R87" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="S87" t="n">
+        <v>8</v>
+      </c>
+      <c r="T87" t="n">
+        <v>4</v>
+      </c>
+      <c r="U87" t="n">
+        <v>15</v>
+      </c>
+      <c r="V87" t="n">
+        <v>11</v>
+      </c>
+      <c r="W87" t="n">
+        <v>12</v>
+      </c>
+      <c r="X87" t="n">
         <v>7</v>
       </c>
-      <c r="T87" t="n">
-        <v>6</v>
-      </c>
-      <c r="U87" t="n">
-        <v>10</v>
-      </c>
-      <c r="V87" t="n">
-        <v>7</v>
-      </c>
-      <c r="W87" t="n">
-        <v>6</v>
-      </c>
-      <c r="X87" t="n">
-        <v>11</v>
-      </c>
       <c r="Y87" t="n">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="Z87" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>Emirates Stadium</t>
+          <t>Molineux Stadium</t>
         </is>
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>Queensland Road, London</t>
+          <t>Waterloo Road, Wolverhampton, West Midlands</t>
         </is>
       </c>
       <c r="AC87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD87" t="n">
         <v>0</v>
       </c>
       <c r="AE87" t="n">
-        <v>1.4</v>
+        <v>1.84</v>
       </c>
       <c r="AF87" t="n">
-        <v>4.86</v>
+        <v>3.25</v>
       </c>
       <c r="AG87" t="n">
-        <v>8.359999999999999</v>
+        <v>3.9</v>
       </c>
       <c r="AH87" t="n">
-        <v>1.25</v>
+        <v>1.39</v>
       </c>
       <c r="AI87" t="n">
-        <v>1.82</v>
+        <v>2.2</v>
       </c>
       <c r="AJ87" t="n">
-        <v>2.92</v>
+        <v>4.15</v>
       </c>
       <c r="AK87" t="n">
-        <v>2.07</v>
+        <v>2</v>
       </c>
       <c r="AL87" t="n">
-        <v>1.81</v>
+        <v>1.71</v>
       </c>
       <c r="AM87" t="n">
-        <v>1.34</v>
+        <v>1.6</v>
       </c>
       <c r="AN87" t="n">
-        <v>1.65</v>
+        <v>1.98</v>
       </c>
       <c r="AO87" t="n">
-        <v>2.97</v>
+        <v>2.2</v>
       </c>
       <c r="AP87" t="n">
-        <v>2.2</v>
+        <v>1.68</v>
       </c>
       <c r="AQ87" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AR87" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AS87" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="AT87" t="n">
         <v>1.3</v>
       </c>
-      <c r="AR87" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AS87" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AT87" t="n">
-        <v>1.49</v>
-      </c>
       <c r="AU87" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="AV87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW87" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX87" t="n">
         <v>0</v>
       </c>
       <c r="AY87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BA87" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BB87" t="n">
-        <v>59</v>
+        <v>145</v>
       </c>
       <c r="BC87" t="n">
         <v>0</v>
       </c>
       <c r="BD87" t="n">
-        <v>38</v>
+        <v>75</v>
       </c>
       <c r="BE87" t="n">
         <v>0</v>
@@ -41758,19 +41758,19 @@
         <v>2</v>
       </c>
       <c r="BH87" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BI87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BJ87" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BK87" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BL87" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BM87" t="n">
         <v>2</v>
@@ -41779,7 +41779,7 @@
         <v>5</v>
       </c>
       <c r="BO87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP87" t="n">
         <v>0</v>
@@ -41791,7 +41791,7 @@
         <v>0</v>
       </c>
       <c r="BS87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT87" t="n">
         <v>0</v>
@@ -41800,34 +41800,34 @@
         <v>1</v>
       </c>
       <c r="BV87" t="n">
-        <v>51</v>
+        <v>64</v>
       </c>
       <c r="BW87" t="n">
-        <v>41</v>
+        <v>29</v>
       </c>
       <c r="BX87" t="n">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="BY87" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="BZ87" t="n">
-        <v>1.22</v>
+        <v>1.91</v>
       </c>
       <c r="CA87" t="n">
-        <v>0.82</v>
+        <v>1.4</v>
       </c>
       <c r="CB87" t="n">
-        <v>2.04</v>
+        <v>3.31</v>
       </c>
       <c r="CC87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD87" t="n">
         <v>0</v>
       </c>
       <c r="CE87" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF87" t="n">
         <v>0</v>
@@ -41857,82 +41857,82 @@
         <v>1</v>
       </c>
       <c r="CO87" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CP87" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CQ87" t="n">
         <v>1</v>
       </c>
       <c r="CR87" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="CS87" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="CT87" t="n">
         <v>1</v>
       </c>
       <c r="CU87" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="CV87" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="CW87" t="n">
         <v>1</v>
       </c>
       <c r="CX87" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="CY87" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="CZ87" t="n">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="DA87" t="n">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="DB87" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC87" t="n">
+        <v>100</v>
+      </c>
+      <c r="DD87" t="n">
+        <v>0.17</v>
+      </c>
+      <c r="DE87" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DF87" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DG87" t="n">
+        <v>0</v>
+      </c>
+      <c r="DH87" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="DI87" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="DJ87" t="n">
         <v>13</v>
       </c>
-      <c r="DC87" t="n">
-        <v>88</v>
-      </c>
-      <c r="DD87" t="n">
-        <v>2.67</v>
-      </c>
-      <c r="DE87" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="DF87" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="DG87" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="DH87" t="n">
-        <v>2.38</v>
-      </c>
-      <c r="DI87" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="DJ87" t="n">
-        <v>38</v>
-      </c>
       <c r="DK87" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="DL87" t="n">
-        <v>1.86</v>
+        <v>1.26</v>
       </c>
       <c r="DM87" t="n">
-        <v>1.37</v>
+        <v>0.95</v>
       </c>
       <c r="DN87" t="n">
-        <v>3.23</v>
+        <v>2.21</v>
       </c>
       <c r="DO87" t="n">
         <v>12</v>
@@ -41941,93 +41941,113 @@
         <v>1</v>
       </c>
       <c r="DQ87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU87" t="b">
         <v>0</v>
       </c>
       <c r="DV87" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW87" t="n">
-        <v>9.06</v>
+        <v>8.119999999999999</v>
       </c>
       <c r="DX87" t="n">
-        <v>6.89</v>
+        <v>9.83</v>
       </c>
       <c r="DY87" t="inlineStr">
         <is>
-          <t>63%</t>
+          <t>72%</t>
         </is>
       </c>
       <c r="DZ87" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="EA87" t="inlineStr">
         <is>
-          <t>1.70</t>
-        </is>
-      </c>
-      <c r="EB87" t="inlineStr">
-        <is>
-          <t>2.75</t>
-        </is>
-      </c>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="EB87" t="inlineStr"/>
       <c r="EC87" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="ED87" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="EE87" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>3.41</t>
         </is>
       </c>
       <c r="EF87" t="inlineStr">
         <is>
-          <t>9.00</t>
+          <t>4.56</t>
         </is>
       </c>
       <c r="EG87" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EH87" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="EI87" t="inlineStr">
         <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="EJ87" t="inlineStr"/>
-      <c r="EK87" t="inlineStr"/>
-      <c r="EL87" t="inlineStr"/>
-      <c r="EM87" t="inlineStr"/>
-      <c r="EN87" t="inlineStr"/>
-      <c r="EO87" t="inlineStr"/>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="EJ87" t="inlineStr">
+        <is>
+          <t>1.63</t>
+        </is>
+      </c>
+      <c r="EK87" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="EL87" t="inlineStr">
+        <is>
+          <t>1.32</t>
+        </is>
+      </c>
+      <c r="EM87" t="inlineStr">
+        <is>
+          <t>1.49</t>
+        </is>
+      </c>
+      <c r="EN87" t="inlineStr">
+        <is>
+          <t>2.68</t>
+        </is>
+      </c>
+      <c r="EO87" t="inlineStr">
+        <is>
+          <t>3.42</t>
+        </is>
+      </c>
       <c r="EP87" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.42</t>
         </is>
       </c>
     </row>
@@ -42047,138 +42067,146 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Manchester City</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F88" s="2" t="n">
         <v>45956.58333333334</v>
       </c>
       <c r="G88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H88" t="n">
         <v>0</v>
       </c>
       <c r="I88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J88" t="n">
+        <v>6</v>
+      </c>
+      <c r="K88" t="n">
+        <v>4</v>
+      </c>
+      <c r="L88" t="n">
+        <v>10</v>
+      </c>
+      <c r="M88" t="n">
+        <v>3</v>
+      </c>
+      <c r="N88" t="n">
+        <v>1</v>
+      </c>
+      <c r="O88" t="n">
+        <v>0</v>
+      </c>
+      <c r="P88" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q88" t="n">
         <v>5</v>
-      </c>
-      <c r="K88" t="n">
-        <v>6</v>
-      </c>
-      <c r="L88" t="n">
-        <v>11</v>
-      </c>
-      <c r="M88" t="n">
-        <v>1</v>
-      </c>
-      <c r="N88" t="n">
-        <v>4</v>
-      </c>
-      <c r="O88" t="n">
-        <v>0</v>
-      </c>
-      <c r="P88" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q88" t="n">
-        <v>3</v>
       </c>
       <c r="R88" t="n">
         <v>4</v>
       </c>
       <c r="S88" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T88" t="n">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="U88" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="V88" t="n">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="W88" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="X88" t="n">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="Y88" t="n">
-        <v>47</v>
+        <v>52</v>
       </c>
       <c r="Z88" t="n">
-        <v>53</v>
-      </c>
-      <c r="AA88" t="inlineStr"/>
-      <c r="AB88" t="inlineStr"/>
+        <v>48</v>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>Vitality Stadium</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>Dean Court, Kings Park, Bournemouth, Dorset</t>
+        </is>
+      </c>
       <c r="AC88" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD88" t="n">
+        <v>1</v>
+      </c>
+      <c r="AE88" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AF88" t="n">
+        <v>3.59</v>
+      </c>
+      <c r="AG88" t="n">
         <v>4</v>
       </c>
-      <c r="AE88" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AF88" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AG88" t="n">
-        <v>1.77</v>
-      </c>
       <c r="AH88" t="n">
-        <v>1.21</v>
+        <v>1.26</v>
       </c>
       <c r="AI88" t="n">
-        <v>1.72</v>
+        <v>1.85</v>
       </c>
       <c r="AJ88" t="n">
-        <v>2.67</v>
+        <v>3.36</v>
       </c>
       <c r="AK88" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="AL88" t="n">
-        <v>2.24</v>
+        <v>2</v>
       </c>
       <c r="AM88" t="n">
-        <v>1.51</v>
+        <v>1.33</v>
       </c>
       <c r="AN88" t="n">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="AO88" t="n">
-        <v>2.54</v>
+        <v>3.3</v>
       </c>
       <c r="AP88" t="n">
-        <v>1.92</v>
+        <v>2.35</v>
       </c>
       <c r="AQ88" t="n">
-        <v>1.3</v>
+        <v>1.36</v>
       </c>
       <c r="AR88" t="n">
-        <v>2.54</v>
+        <v>2.65</v>
       </c>
       <c r="AS88" t="n">
-        <v>3.2</v>
+        <v>2.87</v>
       </c>
       <c r="AT88" t="n">
-        <v>1.5</v>
+        <v>1.42</v>
       </c>
       <c r="AU88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW88" t="n">
         <v>0</v>
@@ -42193,10 +42221,10 @@
         <v>0</v>
       </c>
       <c r="BA88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB88" t="n">
-        <v>158</v>
+        <v>148</v>
       </c>
       <c r="BC88" t="n">
         <v>0</v>
@@ -42217,64 +42245,64 @@
         <v>1</v>
       </c>
       <c r="BI88" t="n">
+        <v>5</v>
+      </c>
+      <c r="BJ88" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK88" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL88" t="n">
         <v>3</v>
       </c>
-      <c r="BJ88" t="n">
-        <v>0</v>
-      </c>
-      <c r="BK88" t="n">
-        <v>2</v>
-      </c>
-      <c r="BL88" t="n">
+      <c r="BM88" t="n">
         <v>6</v>
       </c>
-      <c r="BM88" t="n">
-        <v>3</v>
-      </c>
       <c r="BN88" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="BO88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP88" t="n">
         <v>1</v>
       </c>
       <c r="BQ88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR88" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BS88" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BT88" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BU88" t="n">
         <v>1</v>
       </c>
       <c r="BV88" t="n">
-        <v>29</v>
+        <v>46</v>
       </c>
       <c r="BW88" t="n">
-        <v>69</v>
+        <v>37</v>
       </c>
       <c r="BX88" t="n">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="BY88" t="n">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="BZ88" t="n">
-        <v>1</v>
+        <v>1.51</v>
       </c>
       <c r="CA88" t="n">
-        <v>1.91</v>
+        <v>1.07</v>
       </c>
       <c r="CB88" t="n">
-        <v>2.91</v>
+        <v>2.57</v>
       </c>
       <c r="CC88" t="n">
         <v>0</v>
@@ -42307,7 +42335,7 @@
         <v>0</v>
       </c>
       <c r="CM88" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CN88" t="n">
         <v>0</v>
@@ -42322,19 +42350,19 @@
         <v>1</v>
       </c>
       <c r="CR88" t="n">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="CS88" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="CT88" t="n">
         <v>1</v>
       </c>
       <c r="CU88" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="CV88" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="CW88" t="n">
         <v>1</v>
@@ -42343,52 +42371,52 @@
         <v>7</v>
       </c>
       <c r="CY88" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="CZ88" t="n">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="DA88" t="n">
         <v>75</v>
       </c>
       <c r="DB88" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="DC88" t="n">
-        <v>88</v>
+        <v>63</v>
       </c>
       <c r="DD88" t="n">
-        <v>2.17</v>
+        <v>2.33</v>
       </c>
       <c r="DE88" t="n">
-        <v>1.17</v>
+        <v>0.83</v>
       </c>
       <c r="DF88" t="n">
-        <v>1.75</v>
+        <v>2.5</v>
       </c>
       <c r="DG88" t="n">
-        <v>1.75</v>
+        <v>0.5</v>
       </c>
       <c r="DH88" t="n">
-        <v>1.5</v>
+        <v>1.88</v>
       </c>
       <c r="DI88" t="n">
-        <v>2</v>
+        <v>0.63</v>
       </c>
       <c r="DJ88" t="n">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="DK88" t="n">
         <v>25</v>
       </c>
       <c r="DL88" t="n">
-        <v>1.25</v>
+        <v>1.48</v>
       </c>
       <c r="DM88" t="n">
-        <v>1.26</v>
+        <v>1.17</v>
       </c>
       <c r="DN88" t="n">
-        <v>2.51</v>
+        <v>2.65</v>
       </c>
       <c r="DO88" t="n">
         <v>12</v>
@@ -42397,7 +42425,7 @@
         <v>1</v>
       </c>
       <c r="DQ88" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR88" t="b">
         <v>0</v>
@@ -42415,81 +42443,93 @@
         <v>0</v>
       </c>
       <c r="DW88" t="n">
-        <v>7.74</v>
+        <v>10.42</v>
       </c>
       <c r="DX88" t="n">
-        <v>8.19</v>
+        <v>11.43</v>
       </c>
       <c r="DY88" t="inlineStr">
         <is>
-          <t>71%</t>
+          <t>62%</t>
         </is>
       </c>
       <c r="DZ88" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="EA88" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="EB88" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>3.13</t>
         </is>
       </c>
       <c r="EC88" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="ED88" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.30</t>
         </is>
       </c>
       <c r="EE88" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>3.53</t>
         </is>
       </c>
       <c r="EF88" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="EG88" t="inlineStr">
         <is>
-          <t>4.27</t>
+          <t>2.03</t>
         </is>
       </c>
       <c r="EH88" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.21</t>
         </is>
       </c>
       <c r="EI88" t="inlineStr">
         <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="EJ88" t="inlineStr">
-        <is>
-          <t>1.56</t>
-        </is>
-      </c>
-      <c r="EK88" t="inlineStr">
-        <is>
-          <t>2.39</t>
-        </is>
-      </c>
-      <c r="EL88" t="inlineStr"/>
-      <c r="EM88" t="inlineStr"/>
-      <c r="EN88" t="inlineStr"/>
-      <c r="EO88" t="inlineStr"/>
-      <c r="EP88" t="inlineStr"/>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="EJ88" t="inlineStr"/>
+      <c r="EK88" t="inlineStr"/>
+      <c r="EL88" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EM88" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="EN88" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="EO88" t="inlineStr">
+        <is>
+          <t>2.85</t>
+        </is>
+      </c>
+      <c r="EP88" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -42507,146 +42547,146 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F89" s="2" t="n">
         <v>45956.58333333334</v>
       </c>
       <c r="G89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H89" t="n">
         <v>0</v>
       </c>
       <c r="I89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="J89" t="n">
+        <v>4</v>
+      </c>
+      <c r="K89" t="n">
+        <v>3</v>
+      </c>
+      <c r="L89" t="n">
+        <v>7</v>
+      </c>
+      <c r="M89" t="n">
+        <v>0</v>
+      </c>
+      <c r="N89" t="n">
+        <v>0</v>
+      </c>
+      <c r="O89" t="n">
+        <v>0</v>
+      </c>
+      <c r="P89" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q89" t="n">
+        <v>3</v>
+      </c>
+      <c r="R89" t="n">
+        <v>1</v>
+      </c>
+      <c r="S89" t="n">
+        <v>7</v>
+      </c>
+      <c r="T89" t="n">
         <v>6</v>
       </c>
-      <c r="K89" t="n">
-        <v>4</v>
-      </c>
-      <c r="L89" t="n">
+      <c r="U89" t="n">
         <v>10</v>
       </c>
-      <c r="M89" t="n">
-        <v>3</v>
-      </c>
-      <c r="N89" t="n">
-        <v>1</v>
-      </c>
-      <c r="O89" t="n">
-        <v>0</v>
-      </c>
-      <c r="P89" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q89" t="n">
-        <v>5</v>
-      </c>
-      <c r="R89" t="n">
-        <v>4</v>
-      </c>
-      <c r="S89" t="n">
-        <v>8</v>
-      </c>
-      <c r="T89" t="n">
-        <v>4</v>
-      </c>
-      <c r="U89" t="n">
-        <v>13</v>
-      </c>
       <c r="V89" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W89" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="X89" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="Y89" t="n">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="Z89" t="n">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>Vitality Stadium</t>
+          <t>Emirates Stadium</t>
         </is>
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>Dean Court, Kings Park, Bournemouth, Dorset</t>
+          <t>Queensland Road, London</t>
         </is>
       </c>
       <c r="AC89" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AD89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE89" t="n">
-        <v>1.86</v>
+        <v>1.4</v>
       </c>
       <c r="AF89" t="n">
-        <v>3.59</v>
+        <v>4.86</v>
       </c>
       <c r="AG89" t="n">
-        <v>4</v>
+        <v>8.359999999999999</v>
       </c>
       <c r="AH89" t="n">
-        <v>1.26</v>
+        <v>1.25</v>
       </c>
       <c r="AI89" t="n">
-        <v>1.85</v>
+        <v>1.82</v>
       </c>
       <c r="AJ89" t="n">
-        <v>3.36</v>
+        <v>2.92</v>
       </c>
       <c r="AK89" t="n">
-        <v>1.75</v>
+        <v>2.07</v>
       </c>
       <c r="AL89" t="n">
-        <v>2</v>
+        <v>1.81</v>
       </c>
       <c r="AM89" t="n">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="AN89" t="n">
-        <v>1.76</v>
+        <v>1.65</v>
       </c>
       <c r="AO89" t="n">
-        <v>3.3</v>
+        <v>2.97</v>
       </c>
       <c r="AP89" t="n">
-        <v>2.35</v>
+        <v>2.2</v>
       </c>
       <c r="AQ89" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AR89" t="n">
-        <v>2.65</v>
+        <v>2.5</v>
       </c>
       <c r="AS89" t="n">
-        <v>2.87</v>
+        <v>3.2</v>
       </c>
       <c r="AT89" t="n">
-        <v>1.42</v>
+        <v>1.49</v>
       </c>
       <c r="AU89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AV89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW89" t="n">
         <v>0</v>
@@ -42661,16 +42701,16 @@
         <v>0</v>
       </c>
       <c r="BA89" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB89" t="n">
-        <v>148</v>
+        <v>59</v>
       </c>
       <c r="BC89" t="n">
         <v>0</v>
       </c>
       <c r="BD89" t="n">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="BE89" t="n">
         <v>0</v>
@@ -42682,67 +42722,67 @@
         <v>2</v>
       </c>
       <c r="BH89" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BI89" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ89" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK89" t="n">
+        <v>4</v>
+      </c>
+      <c r="BL89" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM89" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN89" t="n">
         <v>5</v>
       </c>
-      <c r="BJ89" t="n">
-        <v>1</v>
-      </c>
-      <c r="BK89" t="n">
-        <v>1</v>
-      </c>
-      <c r="BL89" t="n">
-        <v>3</v>
-      </c>
-      <c r="BM89" t="n">
-        <v>6</v>
-      </c>
-      <c r="BN89" t="n">
-        <v>4</v>
-      </c>
       <c r="BO89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR89" t="n">
         <v>0</v>
       </c>
       <c r="BS89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BT89" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BU89" t="n">
         <v>1</v>
       </c>
       <c r="BV89" t="n">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="BW89" t="n">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="BX89" t="n">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="BY89" t="n">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="BZ89" t="n">
-        <v>1.51</v>
+        <v>1.22</v>
       </c>
       <c r="CA89" t="n">
-        <v>1.07</v>
+        <v>0.82</v>
       </c>
       <c r="CB89" t="n">
-        <v>2.57</v>
+        <v>2.04</v>
       </c>
       <c r="CC89" t="n">
         <v>0</v>
@@ -42775,22 +42815,22 @@
         <v>0</v>
       </c>
       <c r="CM89" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN89" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CO89" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CP89" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CQ89" t="n">
         <v>1</v>
       </c>
       <c r="CR89" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="CS89" t="n">
         <v>19</v>
@@ -42799,64 +42839,64 @@
         <v>1</v>
       </c>
       <c r="CU89" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="CV89" t="n">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="CW89" t="n">
         <v>1</v>
       </c>
       <c r="CX89" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="CY89" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CZ89" t="n">
-        <v>38</v>
+        <v>63</v>
       </c>
       <c r="DA89" t="n">
-        <v>75</v>
+        <v>88</v>
       </c>
       <c r="DB89" t="n">
         <v>13</v>
       </c>
       <c r="DC89" t="n">
-        <v>63</v>
+        <v>88</v>
       </c>
       <c r="DD89" t="n">
-        <v>2.33</v>
+        <v>2.67</v>
       </c>
       <c r="DE89" t="n">
-        <v>0.83</v>
+        <v>1.67</v>
       </c>
       <c r="DF89" t="n">
         <v>2.5</v>
       </c>
       <c r="DG89" t="n">
-        <v>0.5</v>
+        <v>1.75</v>
       </c>
       <c r="DH89" t="n">
-        <v>1.88</v>
+        <v>2.38</v>
       </c>
       <c r="DI89" t="n">
-        <v>0.63</v>
+        <v>1.63</v>
       </c>
       <c r="DJ89" t="n">
-        <v>63</v>
+        <v>38</v>
       </c>
       <c r="DK89" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="DL89" t="n">
-        <v>1.48</v>
+        <v>1.86</v>
       </c>
       <c r="DM89" t="n">
-        <v>1.17</v>
+        <v>1.37</v>
       </c>
       <c r="DN89" t="n">
-        <v>2.65</v>
+        <v>3.23</v>
       </c>
       <c r="DO89" t="n">
         <v>12</v>
@@ -42865,7 +42905,7 @@
         <v>1</v>
       </c>
       <c r="DQ89" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR89" t="b">
         <v>0</v>
@@ -42883,88 +42923,72 @@
         <v>0</v>
       </c>
       <c r="DW89" t="n">
-        <v>10.42</v>
+        <v>9.06</v>
       </c>
       <c r="DX89" t="n">
-        <v>11.43</v>
+        <v>6.89</v>
       </c>
       <c r="DY89" t="inlineStr">
         <is>
-          <t>62%</t>
+          <t>63%</t>
         </is>
       </c>
       <c r="DZ89" t="inlineStr">
         <is>
-          <t>88%</t>
+          <t>23%</t>
         </is>
       </c>
       <c r="EA89" t="inlineStr">
         <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="EB89" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="EC89" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="ED89" t="inlineStr">
+        <is>
+          <t>2.28</t>
+        </is>
+      </c>
+      <c r="EE89" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="EF89" t="inlineStr">
+        <is>
+          <t>9.00</t>
+        </is>
+      </c>
+      <c r="EG89" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="EH89" t="inlineStr">
+        <is>
           <t>1.87</t>
         </is>
       </c>
-      <c r="EB89" t="inlineStr">
-        <is>
-          <t>3.13</t>
-        </is>
-      </c>
-      <c r="EC89" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
-      </c>
-      <c r="ED89" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
-      </c>
-      <c r="EE89" t="inlineStr">
-        <is>
-          <t>3.53</t>
-        </is>
-      </c>
-      <c r="EF89" t="inlineStr">
-        <is>
-          <t>3.97</t>
-        </is>
-      </c>
-      <c r="EG89" t="inlineStr">
-        <is>
-          <t>2.03</t>
-        </is>
-      </c>
-      <c r="EH89" t="inlineStr">
-        <is>
-          <t>2.21</t>
-        </is>
-      </c>
       <c r="EI89" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="EJ89" t="inlineStr"/>
       <c r="EK89" t="inlineStr"/>
-      <c r="EL89" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="EM89" t="inlineStr">
-        <is>
-          <t>1.38</t>
-        </is>
-      </c>
-      <c r="EN89" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="EO89" t="inlineStr">
-        <is>
-          <t>2.85</t>
-        </is>
-      </c>
+      <c r="EL89" t="inlineStr"/>
+      <c r="EM89" t="inlineStr"/>
+      <c r="EN89" t="inlineStr"/>
+      <c r="EO89" t="inlineStr"/>
       <c r="EP89" t="inlineStr">
         <is>
           <t>1.26</t>
@@ -42987,170 +43011,162 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Manchester City</t>
         </is>
       </c>
       <c r="F90" s="2" t="n">
         <v>45956.58333333334</v>
       </c>
       <c r="G90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H90" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" t="n">
+        <v>1</v>
+      </c>
+      <c r="J90" t="n">
+        <v>5</v>
+      </c>
+      <c r="K90" t="n">
+        <v>6</v>
+      </c>
+      <c r="L90" t="n">
+        <v>11</v>
+      </c>
+      <c r="M90" t="n">
+        <v>1</v>
+      </c>
+      <c r="N90" t="n">
+        <v>4</v>
+      </c>
+      <c r="O90" t="n">
+        <v>0</v>
+      </c>
+      <c r="P90" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q90" t="n">
         <v>3</v>
       </c>
-      <c r="I90" t="n">
-        <v>5</v>
-      </c>
-      <c r="J90" t="n">
+      <c r="R90" t="n">
         <v>4</v>
       </c>
-      <c r="K90" t="n">
-        <v>3</v>
-      </c>
-      <c r="L90" t="n">
-        <v>7</v>
-      </c>
-      <c r="M90" t="n">
-        <v>1</v>
-      </c>
-      <c r="N90" t="n">
-        <v>0</v>
-      </c>
-      <c r="O90" t="n">
-        <v>0</v>
-      </c>
-      <c r="P90" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q90" t="n">
-        <v>7</v>
-      </c>
-      <c r="R90" t="n">
-        <v>7</v>
-      </c>
       <c r="S90" t="n">
+        <v>6</v>
+      </c>
+      <c r="T90" t="n">
+        <v>14</v>
+      </c>
+      <c r="U90" t="n">
+        <v>9</v>
+      </c>
+      <c r="V90" t="n">
+        <v>18</v>
+      </c>
+      <c r="W90" t="n">
         <v>8</v>
       </c>
-      <c r="T90" t="n">
+      <c r="X90" t="n">
+        <v>16</v>
+      </c>
+      <c r="Y90" t="n">
+        <v>47</v>
+      </c>
+      <c r="Z90" t="n">
+        <v>53</v>
+      </c>
+      <c r="AA90" t="inlineStr"/>
+      <c r="AB90" t="inlineStr"/>
+      <c r="AC90" t="n">
+        <v>1</v>
+      </c>
+      <c r="AD90" t="n">
         <v>4</v>
       </c>
-      <c r="U90" t="n">
-        <v>15</v>
-      </c>
-      <c r="V90" t="n">
-        <v>11</v>
-      </c>
-      <c r="W90" t="n">
-        <v>12</v>
-      </c>
-      <c r="X90" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y90" t="n">
-        <v>57</v>
-      </c>
-      <c r="Z90" t="n">
-        <v>43</v>
-      </c>
-      <c r="AA90" t="inlineStr">
-        <is>
-          <t>Molineux Stadium</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>Waterloo Road, Wolverhampton, West Midlands</t>
-        </is>
-      </c>
-      <c r="AC90" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD90" t="n">
-        <v>0</v>
-      </c>
       <c r="AE90" t="n">
-        <v>1.84</v>
+        <v>4.2</v>
       </c>
       <c r="AF90" t="n">
-        <v>3.25</v>
+        <v>3.85</v>
       </c>
       <c r="AG90" t="n">
-        <v>3.9</v>
+        <v>1.77</v>
       </c>
       <c r="AH90" t="n">
-        <v>1.39</v>
+        <v>1.21</v>
       </c>
       <c r="AI90" t="n">
-        <v>2.2</v>
+        <v>1.72</v>
       </c>
       <c r="AJ90" t="n">
-        <v>4.15</v>
+        <v>2.67</v>
       </c>
       <c r="AK90" t="n">
-        <v>2</v>
+        <v>1.68</v>
       </c>
       <c r="AL90" t="n">
-        <v>1.71</v>
+        <v>2.24</v>
       </c>
       <c r="AM90" t="n">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="AN90" t="n">
-        <v>1.98</v>
+        <v>1.73</v>
       </c>
       <c r="AO90" t="n">
-        <v>2.2</v>
+        <v>2.54</v>
       </c>
       <c r="AP90" t="n">
-        <v>1.68</v>
+        <v>1.92</v>
       </c>
       <c r="AQ90" t="n">
-        <v>1.49</v>
+        <v>1.3</v>
       </c>
       <c r="AR90" t="n">
+        <v>2.54</v>
+      </c>
+      <c r="AS90" t="n">
         <v>3.2</v>
       </c>
-      <c r="AS90" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AT90" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="AU90" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AV90" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW90" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX90" t="n">
         <v>0</v>
       </c>
       <c r="AY90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA90" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="BB90" t="n">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="BC90" t="n">
         <v>0</v>
       </c>
       <c r="BD90" t="n">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="BE90" t="n">
         <v>0</v>
@@ -43165,73 +43181,73 @@
         <v>1</v>
       </c>
       <c r="BI90" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BJ90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BK90" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL90" t="n">
+        <v>6</v>
+      </c>
+      <c r="BM90" t="n">
         <v>3</v>
       </c>
-      <c r="BL90" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM90" t="n">
-        <v>2</v>
-      </c>
       <c r="BN90" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="BO90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ90" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR90" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BS90" t="n">
         <v>1</v>
       </c>
       <c r="BT90" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BU90" t="n">
         <v>1</v>
       </c>
       <c r="BV90" t="n">
-        <v>64</v>
+        <v>29</v>
       </c>
       <c r="BW90" t="n">
-        <v>29</v>
+        <v>69</v>
       </c>
       <c r="BX90" t="n">
-        <v>124</v>
+        <v>81</v>
       </c>
       <c r="BY90" t="n">
-        <v>90</v>
+        <v>110</v>
       </c>
       <c r="BZ90" t="n">
+        <v>1</v>
+      </c>
+      <c r="CA90" t="n">
         <v>1.91</v>
       </c>
-      <c r="CA90" t="n">
-        <v>1.4</v>
-      </c>
       <c r="CB90" t="n">
-        <v>3.31</v>
+        <v>2.91</v>
       </c>
       <c r="CC90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD90" t="n">
         <v>0</v>
       </c>
       <c r="CE90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF90" t="n">
         <v>0</v>
@@ -43258,7 +43274,7 @@
         <v>0</v>
       </c>
       <c r="CN90" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CO90" t="n">
         <v>0</v>
@@ -43270,73 +43286,73 @@
         <v>1</v>
       </c>
       <c r="CR90" t="n">
+        <v>13</v>
+      </c>
+      <c r="CS90" t="n">
         <v>14</v>
       </c>
-      <c r="CS90" t="n">
+      <c r="CT90" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU90" t="n">
         <v>18</v>
       </c>
-      <c r="CT90" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU90" t="n">
+      <c r="CV90" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW90" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX90" t="n">
         <v>7</v>
       </c>
-      <c r="CV90" t="n">
-        <v>14</v>
-      </c>
-      <c r="CW90" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX90" t="n">
+      <c r="CY90" t="n">
         <v>3</v>
       </c>
-      <c r="CY90" t="n">
-        <v>10</v>
-      </c>
       <c r="CZ90" t="n">
+        <v>63</v>
+      </c>
+      <c r="DA90" t="n">
+        <v>75</v>
+      </c>
+      <c r="DB90" t="n">
+        <v>25</v>
+      </c>
+      <c r="DC90" t="n">
         <v>88</v>
       </c>
-      <c r="DA90" t="n">
-        <v>100</v>
-      </c>
-      <c r="DB90" t="n">
-        <v>50</v>
-      </c>
-      <c r="DC90" t="n">
-        <v>100</v>
-      </c>
       <c r="DD90" t="n">
-        <v>0.17</v>
+        <v>2.17</v>
       </c>
       <c r="DE90" t="n">
-        <v>0.5</v>
+        <v>1.17</v>
       </c>
       <c r="DF90" t="n">
-        <v>0.25</v>
+        <v>1.75</v>
       </c>
       <c r="DG90" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="DH90" t="n">
-        <v>0.25</v>
+        <v>1.5</v>
       </c>
       <c r="DI90" t="n">
-        <v>0.88</v>
+        <v>2</v>
       </c>
       <c r="DJ90" t="n">
-        <v>13</v>
+        <v>38</v>
       </c>
       <c r="DK90" t="n">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="DL90" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="DM90" t="n">
         <v>1.26</v>
       </c>
-      <c r="DM90" t="n">
-        <v>0.95</v>
-      </c>
       <c r="DN90" t="n">
-        <v>2.21</v>
+        <v>2.51</v>
       </c>
       <c r="DO90" t="n">
         <v>12</v>
@@ -43345,115 +43361,99 @@
         <v>1</v>
       </c>
       <c r="DQ90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU90" t="b">
         <v>0</v>
       </c>
       <c r="DV90" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW90" t="n">
-        <v>8.119999999999999</v>
+        <v>7.74</v>
       </c>
       <c r="DX90" t="n">
-        <v>9.83</v>
+        <v>8.19</v>
       </c>
       <c r="DY90" t="inlineStr">
         <is>
-          <t>72%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="DZ90" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>74%</t>
         </is>
       </c>
       <c r="EA90" t="inlineStr">
         <is>
-          <t>2.32</t>
-        </is>
-      </c>
-      <c r="EB90" t="inlineStr"/>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="EB90" t="inlineStr">
+        <is>
+          <t>2.76</t>
+        </is>
+      </c>
       <c r="EC90" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="ED90" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EE90" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="EF90" t="inlineStr">
         <is>
-          <t>4.56</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EG90" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>4.27</t>
         </is>
       </c>
       <c r="EH90" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="EI90" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="EJ90" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.56</t>
         </is>
       </c>
       <c r="EK90" t="inlineStr">
         <is>
-          <t>2.27</t>
-        </is>
-      </c>
-      <c r="EL90" t="inlineStr">
-        <is>
-          <t>1.32</t>
-        </is>
-      </c>
-      <c r="EM90" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="EN90" t="inlineStr">
-        <is>
-          <t>2.68</t>
-        </is>
-      </c>
-      <c r="EO90" t="inlineStr">
-        <is>
-          <t>3.42</t>
-        </is>
-      </c>
-      <c r="EP90" t="inlineStr">
-        <is>
-          <t>1.42</t>
-        </is>
-      </c>
+          <t>2.39</t>
+        </is>
+      </c>
+      <c r="EL90" t="inlineStr"/>
+      <c r="EM90" t="inlineStr"/>
+      <c r="EN90" t="inlineStr"/>
+      <c r="EO90" t="inlineStr"/>
+      <c r="EP90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -43815,7 +43815,7 @@
         <v>2.91</v>
       </c>
       <c r="DO91" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
@@ -43943,31 +43943,31 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Brighton &amp; Hove Albion</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Leeds United</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="F92" s="2" t="n">
         <v>45962.625</v>
       </c>
       <c r="G92" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H92" t="n">
         <v>0</v>
       </c>
       <c r="I92" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J92" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="K92" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L92" t="n">
         <v>11</v>
@@ -43976,7 +43976,7 @@
         <v>0</v>
       </c>
       <c r="N92" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O92" t="n">
         <v>0</v>
@@ -43985,7 +43985,7 @@
         <v>0</v>
       </c>
       <c r="Q92" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="R92" t="n">
         <v>2</v>
@@ -43994,92 +43994,92 @@
         <v>7</v>
       </c>
       <c r="T92" t="n">
+        <v>4</v>
+      </c>
+      <c r="U92" t="n">
+        <v>10</v>
+      </c>
+      <c r="V92" t="n">
+        <v>6</v>
+      </c>
+      <c r="W92" t="n">
+        <v>7</v>
+      </c>
+      <c r="X92" t="n">
+        <v>11</v>
+      </c>
+      <c r="Y92" t="n">
+        <v>36</v>
+      </c>
+      <c r="Z92" t="n">
+        <v>64</v>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>Selhurst Park</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>Holmesdale Road, London</t>
+        </is>
+      </c>
+      <c r="AC92" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD92" t="n">
         <v>3</v>
       </c>
-      <c r="U92" t="n">
-        <v>14</v>
-      </c>
-      <c r="V92" t="n">
-        <v>5</v>
-      </c>
-      <c r="W92" t="n">
-        <v>10</v>
-      </c>
-      <c r="X92" t="n">
-        <v>7</v>
-      </c>
-      <c r="Y92" t="n">
-        <v>50</v>
-      </c>
-      <c r="Z92" t="n">
-        <v>50</v>
-      </c>
-      <c r="AA92" t="inlineStr">
-        <is>
-          <t>The American Express Community Stadium</t>
-        </is>
-      </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>Village Way, Falmer, East Sussex</t>
-        </is>
-      </c>
-      <c r="AC92" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD92" t="n">
-        <v>1</v>
-      </c>
       <c r="AE92" t="n">
-        <v>1.85</v>
+        <v>2.08</v>
       </c>
       <c r="AF92" t="n">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="AG92" t="n">
         <v>3.65</v>
       </c>
       <c r="AH92" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AI92" t="n">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="AJ92" t="n">
-        <v>3.2</v>
+        <v>2.93</v>
       </c>
       <c r="AK92" t="n">
         <v>1.67</v>
       </c>
       <c r="AL92" t="n">
-        <v>2.1</v>
+        <v>2.24</v>
       </c>
       <c r="AM92" t="n">
-        <v>1.71</v>
+        <v>1.51</v>
       </c>
       <c r="AN92" t="n">
-        <v>2.14</v>
+        <v>1.79</v>
       </c>
       <c r="AO92" t="n">
-        <v>2.05</v>
+        <v>2.39</v>
       </c>
       <c r="AP92" t="n">
-        <v>1.6</v>
+        <v>1.95</v>
       </c>
       <c r="AQ92" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="AR92" t="n">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="AS92" t="n">
         <v>3.2</v>
       </c>
       <c r="AT92" t="n">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="AU92" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV92" t="n">
         <v>1</v>
@@ -44088,25 +44088,25 @@
         <v>0</v>
       </c>
       <c r="AX92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY92" t="n">
         <v>0</v>
       </c>
       <c r="AZ92" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA92" t="n">
         <v>1</v>
       </c>
       <c r="BB92" t="n">
-        <v>209</v>
+        <v>143</v>
       </c>
       <c r="BC92" t="n">
         <v>0</v>
       </c>
       <c r="BD92" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="BE92" t="n">
         <v>0</v>
@@ -44121,133 +44121,133 @@
         <v>1</v>
       </c>
       <c r="BI92" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BJ92" t="n">
         <v>3</v>
       </c>
       <c r="BK92" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BL92" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM92" t="n">
+        <v>7</v>
+      </c>
+      <c r="BN92" t="n">
         <v>4</v>
       </c>
-      <c r="BM92" t="n">
-        <v>4</v>
-      </c>
-      <c r="BN92" t="n">
+      <c r="BO92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP92" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ92" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR92" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS92" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT92" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU92" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV92" t="n">
+        <v>44</v>
+      </c>
+      <c r="BW92" t="n">
+        <v>50</v>
+      </c>
+      <c r="BX92" t="n">
+        <v>79</v>
+      </c>
+      <c r="BY92" t="n">
+        <v>85</v>
+      </c>
+      <c r="BZ92" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="CA92" t="n">
+        <v>0.89</v>
+      </c>
+      <c r="CB92" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="CC92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI92" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ92" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM92" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP92" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ92" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR92" t="n">
+        <v>23</v>
+      </c>
+      <c r="CS92" t="n">
+        <v>19</v>
+      </c>
+      <c r="CT92" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU92" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV92" t="n">
         <v>7</v>
       </c>
-      <c r="BO92" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP92" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ92" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR92" t="n">
-        <v>1</v>
-      </c>
-      <c r="BS92" t="n">
-        <v>0</v>
-      </c>
-      <c r="BT92" t="n">
-        <v>1</v>
-      </c>
-      <c r="BU92" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV92" t="n">
-        <v>35</v>
-      </c>
-      <c r="BW92" t="n">
-        <v>38</v>
-      </c>
-      <c r="BX92" t="n">
-        <v>87</v>
-      </c>
-      <c r="BY92" t="n">
-        <v>79</v>
-      </c>
-      <c r="BZ92" t="n">
-        <v>1.63</v>
-      </c>
-      <c r="CA92" t="n">
-        <v>0.74</v>
-      </c>
-      <c r="CB92" t="n">
-        <v>2.37</v>
-      </c>
-      <c r="CC92" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD92" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE92" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF92" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG92" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH92" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI92" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ92" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK92" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL92" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM92" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN92" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO92" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP92" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ92" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR92" t="n">
-        <v>22</v>
-      </c>
-      <c r="CS92" t="n">
-        <v>18</v>
-      </c>
-      <c r="CT92" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU92" t="n">
-        <v>7</v>
-      </c>
-      <c r="CV92" t="n">
-        <v>10</v>
-      </c>
       <c r="CW92" t="n">
         <v>1</v>
       </c>
       <c r="CX92" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="CY92" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="CZ92" t="n">
         <v>63</v>
@@ -44262,22 +44262,22 @@
         <v>75</v>
       </c>
       <c r="DD92" t="n">
-        <v>2.33</v>
+        <v>1.67</v>
       </c>
       <c r="DE92" t="n">
         <v>0.5</v>
       </c>
       <c r="DF92" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="DG92" t="n">
         <v>0.75</v>
       </c>
       <c r="DH92" t="n">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="DI92" t="n">
-        <v>1.22</v>
+        <v>1.44</v>
       </c>
       <c r="DJ92" t="n">
         <v>38</v>
@@ -44286,13 +44286,13 @@
         <v>13</v>
       </c>
       <c r="DL92" t="n">
-        <v>1.43</v>
+        <v>1.68</v>
       </c>
       <c r="DM92" t="n">
-        <v>1.15</v>
+        <v>1.32</v>
       </c>
       <c r="DN92" t="n">
-        <v>2.58</v>
+        <v>3</v>
       </c>
       <c r="DO92" t="n">
         <v>12</v>
@@ -44304,7 +44304,7 @@
         <v>1</v>
       </c>
       <c r="DR92" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS92" t="b">
         <v>0</v>
@@ -44319,14 +44319,14 @@
         <v>0</v>
       </c>
       <c r="DW92" t="n">
-        <v>12.93</v>
+        <v>11.49</v>
       </c>
       <c r="DX92" t="n">
-        <v>12.87</v>
+        <v>8.66</v>
       </c>
       <c r="DY92" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>94%</t>
         </is>
       </c>
       <c r="DZ92" t="inlineStr">
@@ -44336,57 +44336,57 @@
       </c>
       <c r="EA92" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EB92" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="EC92" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="ED92" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="EE92" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="EF92" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.71</t>
         </is>
       </c>
       <c r="EG92" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>2.14</t>
         </is>
       </c>
       <c r="EH92" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="EI92" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="EJ92" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="EK92" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="EL92" t="inlineStr">
@@ -44401,17 +44401,17 @@
       </c>
       <c r="EN92" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>3.18</t>
         </is>
       </c>
       <c r="EO92" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="EP92" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.27</t>
         </is>
       </c>
     </row>
@@ -44431,170 +44431,170 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Burnley</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Arsenal</t>
         </is>
       </c>
       <c r="F93" s="2" t="n">
         <v>45962.625</v>
       </c>
       <c r="G93" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I93" t="n">
         <v>2</v>
       </c>
       <c r="J93" t="n">
+        <v>1</v>
+      </c>
+      <c r="K93" t="n">
         <v>6</v>
       </c>
-      <c r="K93" t="n">
-        <v>5</v>
-      </c>
       <c r="L93" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="M93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N93" t="n">
+        <v>1</v>
+      </c>
+      <c r="O93" t="n">
+        <v>0</v>
+      </c>
+      <c r="P93" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q93" t="n">
+        <v>0</v>
+      </c>
+      <c r="R93" t="n">
+        <v>8</v>
+      </c>
+      <c r="S93" t="n">
         <v>3</v>
-      </c>
-      <c r="O93" t="n">
-        <v>0</v>
-      </c>
-      <c r="P93" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q93" t="n">
-        <v>3</v>
-      </c>
-      <c r="R93" t="n">
-        <v>2</v>
-      </c>
-      <c r="S93" t="n">
-        <v>7</v>
       </c>
       <c r="T93" t="n">
         <v>4</v>
       </c>
       <c r="U93" t="n">
+        <v>3</v>
+      </c>
+      <c r="V93" t="n">
+        <v>12</v>
+      </c>
+      <c r="W93" t="n">
         <v>10</v>
       </c>
-      <c r="V93" t="n">
-        <v>6</v>
-      </c>
-      <c r="W93" t="n">
-        <v>7</v>
-      </c>
       <c r="X93" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="Y93" t="n">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="Z93" t="n">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>Selhurst Park</t>
+          <t>Turf Moor</t>
         </is>
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>Holmesdale Road, London</t>
+          <t>Harry Potts Way, Burnley</t>
         </is>
       </c>
       <c r="AC93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD93" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE93" t="n">
-        <v>2.08</v>
+        <v>12</v>
       </c>
       <c r="AF93" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="AG93" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AH93" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AI93" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AJ93" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="AK93" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="AL93" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="AM93" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AN93" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AO93" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="AP93" t="n">
+        <v>2.16</v>
+      </c>
+      <c r="AQ93" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AR93" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AS93" t="n">
         <v>3.35</v>
       </c>
-      <c r="AG93" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="AH93" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI93" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AJ93" t="n">
-        <v>2.93</v>
-      </c>
-      <c r="AK93" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="AL93" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AM93" t="n">
-        <v>1.51</v>
-      </c>
-      <c r="AN93" t="n">
-        <v>1.79</v>
-      </c>
-      <c r="AO93" t="n">
-        <v>2.39</v>
-      </c>
-      <c r="AP93" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AQ93" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AR93" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AS93" t="n">
-        <v>3.2</v>
-      </c>
       <c r="AT93" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="AU93" t="n">
         <v>2</v>
       </c>
       <c r="AV93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW93" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY93" t="n">
         <v>0</v>
       </c>
       <c r="AZ93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BA93" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB93" t="n">
-        <v>143</v>
+        <v>59</v>
       </c>
       <c r="BC93" t="n">
         <v>0</v>
       </c>
       <c r="BD93" t="n">
-        <v>75</v>
+        <v>25</v>
       </c>
       <c r="BE93" t="n">
         <v>0</v>
@@ -44609,34 +44609,34 @@
         <v>1</v>
       </c>
       <c r="BI93" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ93" t="n">
         <v>4</v>
       </c>
-      <c r="BJ93" t="n">
+      <c r="BK93" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL93" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM93" t="n">
+        <v>4</v>
+      </c>
+      <c r="BN93" t="n">
         <v>3</v>
       </c>
-      <c r="BK93" t="n">
-        <v>2</v>
-      </c>
-      <c r="BL93" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM93" t="n">
-        <v>7</v>
-      </c>
-      <c r="BN93" t="n">
-        <v>4</v>
-      </c>
       <c r="BO93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BR93" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BS93" t="n">
         <v>1</v>
@@ -44648,139 +44648,139 @@
         <v>1</v>
       </c>
       <c r="BV93" t="n">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="BW93" t="n">
+        <v>38</v>
+      </c>
+      <c r="BX93" t="n">
+        <v>100</v>
+      </c>
+      <c r="BY93" t="n">
+        <v>79</v>
+      </c>
+      <c r="BZ93" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="CA93" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="CB93" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="CC93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI93" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ93" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP93" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ93" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR93" t="n">
+        <v>19</v>
+      </c>
+      <c r="CS93" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT93" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU93" t="n">
+        <v>13</v>
+      </c>
+      <c r="CV93" t="n">
+        <v>10</v>
+      </c>
+      <c r="CW93" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX93" t="n">
+        <v>9</v>
+      </c>
+      <c r="CY93" t="n">
+        <v>2</v>
+      </c>
+      <c r="CZ93" t="n">
+        <v>13</v>
+      </c>
+      <c r="DA93" t="n">
         <v>50</v>
       </c>
-      <c r="BX93" t="n">
-        <v>79</v>
-      </c>
-      <c r="BY93" t="n">
-        <v>85</v>
-      </c>
-      <c r="BZ93" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="CA93" t="n">
-        <v>0.89</v>
-      </c>
-      <c r="CB93" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="CC93" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD93" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE93" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF93" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG93" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH93" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI93" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ93" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK93" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL93" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM93" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN93" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO93" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP93" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ93" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR93" t="n">
-        <v>23</v>
-      </c>
-      <c r="CS93" t="n">
-        <v>19</v>
-      </c>
-      <c r="CT93" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU93" t="n">
-        <v>11</v>
-      </c>
-      <c r="CV93" t="n">
-        <v>7</v>
-      </c>
-      <c r="CW93" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX93" t="n">
-        <v>8</v>
-      </c>
-      <c r="CY93" t="n">
-        <v>5</v>
-      </c>
-      <c r="CZ93" t="n">
-        <v>63</v>
-      </c>
-      <c r="DA93" t="n">
+      <c r="DB93" t="n">
+        <v>13</v>
+      </c>
+      <c r="DC93" t="n">
+        <v>50</v>
+      </c>
+      <c r="DD93" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DE93" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="DF93" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="DG93" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="DH93" t="n">
+        <v>1.11</v>
+      </c>
+      <c r="DI93" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="DJ93" t="n">
         <v>88</v>
       </c>
-      <c r="DB93" t="n">
-        <v>38</v>
-      </c>
-      <c r="DC93" t="n">
-        <v>75</v>
-      </c>
-      <c r="DD93" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="DE93" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="DF93" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="DG93" t="n">
-        <v>0.75</v>
-      </c>
-      <c r="DH93" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="DI93" t="n">
-        <v>1.44</v>
-      </c>
-      <c r="DJ93" t="n">
-        <v>38</v>
-      </c>
       <c r="DK93" t="n">
-        <v>13</v>
+        <v>50</v>
       </c>
       <c r="DL93" t="n">
-        <v>1.68</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="DM93" t="n">
-        <v>1.32</v>
+        <v>1.57</v>
       </c>
       <c r="DN93" t="n">
-        <v>3</v>
+        <v>2.38</v>
       </c>
       <c r="DO93" t="n">
         <v>12</v>
@@ -44807,99 +44807,99 @@
         <v>0</v>
       </c>
       <c r="DW93" t="n">
-        <v>11.49</v>
+        <v>10.48</v>
       </c>
       <c r="DX93" t="n">
-        <v>8.66</v>
+        <v>11.62</v>
       </c>
       <c r="DY93" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>83%</t>
         </is>
       </c>
       <c r="DZ93" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="EA93" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="EB93" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>3.31</t>
         </is>
       </c>
       <c r="EC93" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="ED93" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>1.98</t>
         </is>
       </c>
       <c r="EE93" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>6.50</t>
         </is>
       </c>
       <c r="EF93" t="inlineStr">
         <is>
-          <t>3.71</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="EG93" t="inlineStr">
         <is>
-          <t>2.14</t>
+          <t>13.50</t>
         </is>
       </c>
       <c r="EH93" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="EI93" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>2.87</t>
         </is>
       </c>
       <c r="EJ93" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.49</t>
         </is>
       </c>
       <c r="EK93" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="EL93" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.42</t>
         </is>
       </c>
       <c r="EM93" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="EN93" t="inlineStr">
         <is>
-          <t>3.18</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="EO93" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.85</t>
         </is>
       </c>
       <c r="EP93" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.29</t>
         </is>
       </c>
     </row>
@@ -44919,170 +44919,170 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Burnley</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>Arsenal</t>
+          <t>Manchester United</t>
         </is>
       </c>
       <c r="F94" s="2" t="n">
         <v>45962.625</v>
       </c>
       <c r="G94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H94" t="n">
         <v>2</v>
       </c>
       <c r="I94" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J94" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K94" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L94" t="n">
+        <v>13</v>
+      </c>
+      <c r="M94" t="n">
+        <v>1</v>
+      </c>
+      <c r="N94" t="n">
+        <v>1</v>
+      </c>
+      <c r="O94" t="n">
+        <v>0</v>
+      </c>
+      <c r="P94" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q94" t="n">
+        <v>3</v>
+      </c>
+      <c r="R94" t="n">
         <v>7</v>
       </c>
-      <c r="M94" t="n">
-        <v>2</v>
-      </c>
-      <c r="N94" t="n">
-        <v>1</v>
-      </c>
-      <c r="O94" t="n">
-        <v>0</v>
-      </c>
-      <c r="P94" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q94" t="n">
-        <v>0</v>
-      </c>
-      <c r="R94" t="n">
-        <v>8</v>
-      </c>
       <c r="S94" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
       <c r="T94" t="n">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="U94" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="V94" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="W94" t="n">
         <v>10</v>
       </c>
       <c r="X94" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="Y94" t="n">
-        <v>46</v>
+        <v>41</v>
       </c>
       <c r="Z94" t="n">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>Turf Moor</t>
+          <t>The City Ground</t>
         </is>
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>Harry Potts Way, Burnley</t>
+          <t>Pavilion Road, Nottingham, Nottinghamshire</t>
         </is>
       </c>
       <c r="AC94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AD94" t="n">
         <v>1</v>
       </c>
       <c r="AE94" t="n">
-        <v>12</v>
+        <v>3.2</v>
       </c>
       <c r="AF94" t="n">
-        <v>5.5</v>
+        <v>3.6</v>
       </c>
       <c r="AG94" t="n">
-        <v>1.25</v>
+        <v>2.07</v>
       </c>
       <c r="AH94" t="n">
-        <v>1.28</v>
+        <v>1.22</v>
       </c>
       <c r="AI94" t="n">
-        <v>1.71</v>
+        <v>1.75</v>
       </c>
       <c r="AJ94" t="n">
-        <v>2.88</v>
+        <v>2.75</v>
       </c>
       <c r="AK94" t="n">
-        <v>2.3</v>
+        <v>1.6</v>
       </c>
       <c r="AL94" t="n">
-        <v>1.57</v>
+        <v>2.35</v>
       </c>
       <c r="AM94" t="n">
         <v>1.36</v>
       </c>
       <c r="AN94" t="n">
-        <v>1.87</v>
+        <v>1.77</v>
       </c>
       <c r="AO94" t="n">
         <v>2.85</v>
       </c>
       <c r="AP94" t="n">
-        <v>2.16</v>
+        <v>2.15</v>
       </c>
       <c r="AQ94" t="n">
-        <v>1.28</v>
+        <v>1.34</v>
       </c>
       <c r="AR94" t="n">
-        <v>2.61</v>
+        <v>2.4</v>
       </c>
       <c r="AS94" t="n">
-        <v>3.35</v>
+        <v>3.36</v>
       </c>
       <c r="AT94" t="n">
-        <v>1.5</v>
+        <v>1.52</v>
       </c>
       <c r="AU94" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV94" t="n">
         <v>0</v>
       </c>
       <c r="AW94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AX94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ94" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BA94" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB94" t="n">
-        <v>59</v>
+        <v>-1</v>
       </c>
       <c r="BC94" t="n">
         <v>0</v>
       </c>
       <c r="BD94" t="n">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="BE94" t="n">
         <v>0</v>
@@ -45097,25 +45097,25 @@
         <v>1</v>
       </c>
       <c r="BI94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BJ94" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BK94" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="BL94" t="n">
         <v>2</v>
       </c>
       <c r="BM94" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BN94" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="BO94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP94" t="n">
         <v>0</v>
@@ -45127,7 +45127,7 @@
         <v>1</v>
       </c>
       <c r="BS94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT94" t="n">
         <v>2</v>
@@ -45136,25 +45136,25 @@
         <v>1</v>
       </c>
       <c r="BV94" t="n">
-        <v>38</v>
+        <v>52</v>
       </c>
       <c r="BW94" t="n">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="BX94" t="n">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="BY94" t="n">
-        <v>79</v>
+        <v>110</v>
       </c>
       <c r="BZ94" t="n">
-        <v>0.48</v>
+        <v>1.66</v>
       </c>
       <c r="CA94" t="n">
-        <v>1.59</v>
+        <v>1.93</v>
       </c>
       <c r="CB94" t="n">
-        <v>2.08</v>
+        <v>3.58</v>
       </c>
       <c r="CC94" t="n">
         <v>0</v>
@@ -45187,10 +45187,10 @@
         <v>0</v>
       </c>
       <c r="CM94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CN94" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="CO94" t="n">
         <v>0</v>
@@ -45202,16 +45202,16 @@
         <v>1</v>
       </c>
       <c r="CR94" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="CS94" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="CT94" t="n">
         <v>1</v>
       </c>
       <c r="CU94" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="CV94" t="n">
         <v>10</v>
@@ -45220,55 +45220,55 @@
         <v>1</v>
       </c>
       <c r="CX94" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY94" t="n">
         <v>9</v>
       </c>
-      <c r="CY94" t="n">
-        <v>2</v>
-      </c>
       <c r="CZ94" t="n">
-        <v>13</v>
+        <v>75</v>
       </c>
       <c r="DA94" t="n">
-        <v>50</v>
+        <v>88</v>
       </c>
       <c r="DB94" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="DC94" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="DD94" t="n">
         <v>1.17</v>
       </c>
       <c r="DE94" t="n">
-        <v>2.17</v>
+        <v>1</v>
       </c>
       <c r="DF94" t="n">
-        <v>1.75</v>
+        <v>0.75</v>
       </c>
       <c r="DG94" t="n">
-        <v>2.25</v>
+        <v>1</v>
       </c>
       <c r="DH94" t="n">
-        <v>1.11</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="DI94" t="n">
-        <v>2.44</v>
+        <v>1.78</v>
       </c>
       <c r="DJ94" t="n">
-        <v>88</v>
+        <v>25</v>
       </c>
       <c r="DK94" t="n">
-        <v>50</v>
+        <v>13</v>
       </c>
       <c r="DL94" t="n">
-        <v>0.8100000000000001</v>
+        <v>1.68</v>
       </c>
       <c r="DM94" t="n">
-        <v>1.57</v>
+        <v>1.34</v>
       </c>
       <c r="DN94" t="n">
-        <v>2.38</v>
+        <v>3.02</v>
       </c>
       <c r="DO94" t="n">
         <v>12</v>
@@ -45280,10 +45280,10 @@
         <v>1</v>
       </c>
       <c r="DR94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT94" t="b">
         <v>0</v>
@@ -45292,104 +45292,92 @@
         <v>0</v>
       </c>
       <c r="DV94" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW94" t="n">
-        <v>10.48</v>
+        <v>11.69</v>
       </c>
       <c r="DX94" t="n">
-        <v>11.62</v>
+        <v>9.880000000000001</v>
       </c>
       <c r="DY94" t="inlineStr">
         <is>
-          <t>83%</t>
+          <t>80%</t>
         </is>
       </c>
       <c r="DZ94" t="inlineStr">
         <is>
-          <t>87%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EA94" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="EB94" t="inlineStr">
         <is>
-          <t>3.31</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="EC94" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="ED94" t="inlineStr">
         <is>
-          <t>1.98</t>
+          <t>2.07</t>
         </is>
       </c>
       <c r="EE94" t="inlineStr">
         <is>
-          <t>6.50</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="EF94" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="EG94" t="inlineStr">
         <is>
-          <t>13.50</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="EH94" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="EI94" t="inlineStr">
         <is>
-          <t>2.87</t>
-        </is>
-      </c>
-      <c r="EJ94" t="inlineStr">
-        <is>
-          <t>1.49</t>
-        </is>
-      </c>
-      <c r="EK94" t="inlineStr">
-        <is>
-          <t>2.58</t>
-        </is>
-      </c>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="EJ94" t="inlineStr"/>
+      <c r="EK94" t="inlineStr"/>
       <c r="EL94" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="EM94" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.34</t>
         </is>
       </c>
       <c r="EN94" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="EO94" t="inlineStr">
         <is>
-          <t>2.85</t>
-        </is>
-      </c>
-      <c r="EP94" t="inlineStr">
-        <is>
-          <t>1.29</t>
-        </is>
-      </c>
+          <t>2.57</t>
+        </is>
+      </c>
+      <c r="EP94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -45407,64 +45395,64 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Brighton &amp; Hove Albion</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Manchester United</t>
+          <t>Leeds United</t>
         </is>
       </c>
       <c r="F95" s="2" t="n">
         <v>45962.625</v>
       </c>
       <c r="G95" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I95" t="n">
+        <v>3</v>
+      </c>
+      <c r="J95" t="n">
         <v>4</v>
       </c>
-      <c r="J95" t="n">
-        <v>8</v>
-      </c>
       <c r="K95" t="n">
+        <v>7</v>
+      </c>
+      <c r="L95" t="n">
+        <v>11</v>
+      </c>
+      <c r="M95" t="n">
+        <v>0</v>
+      </c>
+      <c r="N95" t="n">
+        <v>1</v>
+      </c>
+      <c r="O95" t="n">
+        <v>0</v>
+      </c>
+      <c r="P95" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q95" t="n">
+        <v>7</v>
+      </c>
+      <c r="R95" t="n">
+        <v>2</v>
+      </c>
+      <c r="S95" t="n">
+        <v>7</v>
+      </c>
+      <c r="T95" t="n">
+        <v>3</v>
+      </c>
+      <c r="U95" t="n">
+        <v>14</v>
+      </c>
+      <c r="V95" t="n">
         <v>5</v>
-      </c>
-      <c r="L95" t="n">
-        <v>13</v>
-      </c>
-      <c r="M95" t="n">
-        <v>1</v>
-      </c>
-      <c r="N95" t="n">
-        <v>1</v>
-      </c>
-      <c r="O95" t="n">
-        <v>0</v>
-      </c>
-      <c r="P95" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q95" t="n">
-        <v>3</v>
-      </c>
-      <c r="R95" t="n">
-        <v>7</v>
-      </c>
-      <c r="S95" t="n">
-        <v>14</v>
-      </c>
-      <c r="T95" t="n">
-        <v>11</v>
-      </c>
-      <c r="U95" t="n">
-        <v>17</v>
-      </c>
-      <c r="V95" t="n">
-        <v>18</v>
       </c>
       <c r="W95" t="n">
         <v>10</v>
@@ -45473,104 +45461,104 @@
         <v>7</v>
       </c>
       <c r="Y95" t="n">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="Z95" t="n">
-        <v>59</v>
+        <v>50</v>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>The City Ground</t>
+          <t>The American Express Community Stadium</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>Pavilion Road, Nottingham, Nottinghamshire</t>
+          <t>Village Way, Falmer, East Sussex</t>
         </is>
       </c>
       <c r="AC95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD95" t="n">
         <v>1</v>
       </c>
       <c r="AE95" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AF95" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="AG95" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="AH95" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI95" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AJ95" t="n">
         <v>3.2</v>
       </c>
-      <c r="AF95" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="AG95" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="AH95" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AI95" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="AJ95" t="n">
-        <v>2.75</v>
-      </c>
       <c r="AK95" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL95" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="AM95" t="n">
+        <v>1.71</v>
+      </c>
+      <c r="AN95" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AO95" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AP95" t="n">
         <v>1.6</v>
       </c>
-      <c r="AL95" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="AM95" t="n">
+      <c r="AQ95" t="n">
         <v>1.36</v>
       </c>
-      <c r="AN95" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AO95" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="AP95" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="AQ95" t="n">
-        <v>1.34</v>
-      </c>
       <c r="AR95" t="n">
-        <v>2.4</v>
+        <v>2.48</v>
       </c>
       <c r="AS95" t="n">
-        <v>3.36</v>
+        <v>3.2</v>
       </c>
       <c r="AT95" t="n">
-        <v>1.52</v>
+        <v>1.44</v>
       </c>
       <c r="AU95" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX95" t="n">
         <v>2</v>
       </c>
       <c r="AY95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ95" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA95" t="n">
         <v>1</v>
       </c>
       <c r="BB95" t="n">
-        <v>-1</v>
+        <v>209</v>
       </c>
       <c r="BC95" t="n">
         <v>0</v>
       </c>
       <c r="BD95" t="n">
-        <v>50</v>
+        <v>63</v>
       </c>
       <c r="BE95" t="n">
         <v>0</v>
@@ -45585,22 +45573,22 @@
         <v>1</v>
       </c>
       <c r="BI95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BJ95" t="n">
         <v>3</v>
       </c>
       <c r="BK95" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="BL95" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BM95" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BN95" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BO95" t="n">
         <v>0</v>
@@ -45609,7 +45597,7 @@
         <v>0</v>
       </c>
       <c r="BQ95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR95" t="n">
         <v>1</v>
@@ -45618,31 +45606,31 @@
         <v>0</v>
       </c>
       <c r="BT95" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BU95" t="n">
         <v>1</v>
       </c>
       <c r="BV95" t="n">
-        <v>52</v>
+        <v>35</v>
       </c>
       <c r="BW95" t="n">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="BX95" t="n">
-        <v>101</v>
+        <v>87</v>
       </c>
       <c r="BY95" t="n">
-        <v>110</v>
+        <v>79</v>
       </c>
       <c r="BZ95" t="n">
-        <v>1.66</v>
+        <v>1.63</v>
       </c>
       <c r="CA95" t="n">
-        <v>1.93</v>
+        <v>0.74</v>
       </c>
       <c r="CB95" t="n">
-        <v>3.58</v>
+        <v>2.37</v>
       </c>
       <c r="CC95" t="n">
         <v>0</v>
@@ -45675,10 +45663,10 @@
         <v>0</v>
       </c>
       <c r="CM95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CN95" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CO95" t="n">
         <v>0</v>
@@ -45690,10 +45678,10 @@
         <v>1</v>
       </c>
       <c r="CR95" t="n">
-        <v>15</v>
+        <v>22</v>
       </c>
       <c r="CS95" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="CT95" t="n">
         <v>1</v>
@@ -45708,58 +45696,58 @@
         <v>1</v>
       </c>
       <c r="CX95" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="CY95" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="CZ95" t="n">
-        <v>75</v>
+        <v>63</v>
       </c>
       <c r="DA95" t="n">
         <v>88</v>
       </c>
       <c r="DB95" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="DC95" t="n">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="DD95" t="n">
-        <v>1.17</v>
+        <v>2.33</v>
       </c>
       <c r="DE95" t="n">
-        <v>1</v>
+        <v>0.5</v>
       </c>
       <c r="DF95" t="n">
+        <v>2</v>
+      </c>
+      <c r="DG95" t="n">
         <v>0.75</v>
       </c>
-      <c r="DG95" t="n">
-        <v>1</v>
-      </c>
       <c r="DH95" t="n">
-        <v>0.5600000000000001</v>
+        <v>1.33</v>
       </c>
       <c r="DI95" t="n">
-        <v>1.78</v>
+        <v>1.22</v>
       </c>
       <c r="DJ95" t="n">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="DK95" t="n">
         <v>13</v>
       </c>
       <c r="DL95" t="n">
-        <v>1.68</v>
+        <v>1.43</v>
       </c>
       <c r="DM95" t="n">
-        <v>1.34</v>
+        <v>1.15</v>
       </c>
       <c r="DN95" t="n">
-        <v>3.02</v>
+        <v>2.58</v>
       </c>
       <c r="DO95" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP95" t="b">
         <v>1</v>
@@ -45771,7 +45759,7 @@
         <v>1</v>
       </c>
       <c r="DS95" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT95" t="b">
         <v>0</v>
@@ -45780,17 +45768,17 @@
         <v>0</v>
       </c>
       <c r="DV95" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW95" t="n">
-        <v>11.69</v>
+        <v>12.93</v>
       </c>
       <c r="DX95" t="n">
-        <v>9.880000000000001</v>
+        <v>12.87</v>
       </c>
       <c r="DY95" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="DZ95" t="inlineStr">
@@ -45800,72 +45788,84 @@
       </c>
       <c r="EA95" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="EB95" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="EC95" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="ED95" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="EE95" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="EF95" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="EG95" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="EH95" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="EI95" t="inlineStr">
         <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="EJ95" t="inlineStr"/>
-      <c r="EK95" t="inlineStr"/>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="EJ95" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="EK95" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
       <c r="EL95" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="EM95" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="EN95" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="EO95" t="inlineStr">
         <is>
-          <t>2.57</t>
-        </is>
-      </c>
-      <c r="EP95" t="inlineStr"/>
+          <t>2.78</t>
+        </is>
+      </c>
+      <c r="EP95" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -48581,7 +48581,7 @@
         <v>2</v>
       </c>
       <c r="DE101" t="n">
-        <v>0.8</v>
+        <v>1.17</v>
       </c>
       <c r="DF101" t="n">
         <v>2.5</v>
@@ -48611,7 +48611,7 @@
         <v>2.15</v>
       </c>
       <c r="DO101" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP101" t="b">
         <v>1</v>
@@ -49087,7 +49087,7 @@
         <v>2.6</v>
       </c>
       <c r="DO102" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP102" t="b">
         <v>1</v>
@@ -50027,7 +50027,7 @@
         <v>2.85</v>
       </c>
       <c r="DO104" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="DP104" t="b">
         <v>1</v>
@@ -51083,22 +51083,22 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Aston Villa</t>
+          <t>Brentford</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AFC Bournemouth</t>
+          <t>Newcastle United</t>
         </is>
       </c>
       <c r="F107" s="2" t="n">
         <v>45970.58333333334</v>
       </c>
       <c r="G107" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I107" t="n">
         <v>4</v>
@@ -51107,10 +51107,10 @@
         <v>6</v>
       </c>
       <c r="K107" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="L107" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="M107" t="n">
         <v>2</v>
@@ -51122,37 +51122,37 @@
         <v>0</v>
       </c>
       <c r="P107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q107" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="R107" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="S107" t="n">
         <v>8</v>
       </c>
       <c r="T107" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="U107" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="V107" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="W107" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="X107" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="Y107" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="Z107" t="n">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="AA107" t="inlineStr"/>
       <c r="AB107" t="inlineStr"/>
@@ -51160,25 +51160,25 @@
         <v>2</v>
       </c>
       <c r="AD107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AE107" t="n">
-        <v>2.3</v>
+        <v>2.85</v>
       </c>
       <c r="AF107" t="n">
         <v>3.3</v>
       </c>
       <c r="AG107" t="n">
-        <v>2.85</v>
+        <v>2.45</v>
       </c>
       <c r="AH107" t="n">
-        <v>1.28</v>
+        <v>1.24</v>
       </c>
       <c r="AI107" t="n">
-        <v>1.87</v>
+        <v>1.82</v>
       </c>
       <c r="AJ107" t="n">
-        <v>3.2</v>
+        <v>2.88</v>
       </c>
       <c r="AK107" t="n">
         <v>1.65</v>
@@ -51187,58 +51187,58 @@
         <v>2.15</v>
       </c>
       <c r="AM107" t="n">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="AN107" t="n">
-        <v>1.8</v>
+        <v>1.87</v>
       </c>
       <c r="AO107" t="n">
-        <v>2.78</v>
+        <v>2.83</v>
       </c>
       <c r="AP107" t="n">
-        <v>2.17</v>
+        <v>2.1</v>
       </c>
       <c r="AQ107" t="n">
-        <v>1.33</v>
+        <v>1.38</v>
       </c>
       <c r="AR107" t="n">
         <v>2.6</v>
       </c>
       <c r="AS107" t="n">
-        <v>3.1</v>
+        <v>3.02</v>
       </c>
       <c r="AT107" t="n">
-        <v>1.42</v>
+        <v>1.45</v>
       </c>
       <c r="AU107" t="n">
         <v>4</v>
       </c>
       <c r="AV107" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AW107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AY107" t="n">
         <v>0</v>
       </c>
       <c r="AZ107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA107" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BB107" t="n">
-        <v>158</v>
+        <v>218</v>
       </c>
       <c r="BC107" t="n">
         <v>0</v>
       </c>
       <c r="BD107" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BE107" t="n">
         <v>0</v>
@@ -51253,73 +51253,73 @@
         <v>1</v>
       </c>
       <c r="BI107" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BJ107" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BK107" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BL107" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="BM107" t="n">
         <v>4</v>
       </c>
       <c r="BN107" t="n">
-        <v>11</v>
+        <v>3</v>
       </c>
       <c r="BO107" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BP107" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BQ107" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BR107" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BS107" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BT107" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="BU107" t="n">
         <v>1</v>
       </c>
       <c r="BV107" t="n">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="BW107" t="n">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="BX107" t="n">
-        <v>78</v>
+        <v>101</v>
       </c>
       <c r="BY107" t="n">
-        <v>77</v>
+        <v>92</v>
       </c>
       <c r="BZ107" t="n">
-        <v>1.83</v>
+        <v>1.77</v>
       </c>
       <c r="CA107" t="n">
-        <v>1.26</v>
+        <v>0.65</v>
       </c>
       <c r="CB107" t="n">
-        <v>3.09</v>
+        <v>2.42</v>
       </c>
       <c r="CC107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CD107" t="n">
         <v>0</v>
       </c>
       <c r="CE107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CF107" t="n">
         <v>0</v>
@@ -51358,73 +51358,73 @@
         <v>1</v>
       </c>
       <c r="CR107" t="n">
-        <v>15</v>
+        <v>26</v>
       </c>
       <c r="CS107" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="CT107" t="n">
         <v>1</v>
       </c>
       <c r="CU107" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="CV107" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW107" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX107" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY107" t="n">
         <v>7</v>
       </c>
-      <c r="CW107" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX107" t="n">
-        <v>7</v>
-      </c>
-      <c r="CY107" t="n">
-        <v>4</v>
-      </c>
       <c r="CZ107" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA107" t="n">
+        <v>50</v>
+      </c>
+      <c r="DB107" t="n">
+        <v>30</v>
+      </c>
+      <c r="DC107" t="n">
         <v>70</v>
-      </c>
-      <c r="DA107" t="n">
-        <v>70</v>
-      </c>
-      <c r="DB107" t="n">
-        <v>40</v>
-      </c>
-      <c r="DC107" t="n">
-        <v>90</v>
       </c>
       <c r="DD107" t="n">
         <v>2.17</v>
       </c>
       <c r="DE107" t="n">
-        <v>0.83</v>
+        <v>0.5</v>
       </c>
       <c r="DF107" t="n">
         <v>2</v>
       </c>
       <c r="DG107" t="n">
-        <v>1</v>
+        <v>0.6</v>
       </c>
       <c r="DH107" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="DI107" t="n">
-        <v>1.8</v>
+        <v>1.2</v>
       </c>
       <c r="DJ107" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="DK107" t="n">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="DL107" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="DM107" t="n">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="DN107" t="n">
-        <v>2.62</v>
+        <v>2.65</v>
       </c>
       <c r="DO107" t="n">
         <v>12</v>
@@ -51448,94 +51448,78 @@
         <v>0</v>
       </c>
       <c r="DV107" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW107" t="n">
-        <v>11.54</v>
+        <v>12.74</v>
       </c>
       <c r="DX107" t="n">
-        <v>5.01</v>
+        <v>4.53</v>
       </c>
       <c r="DY107" t="inlineStr">
         <is>
-          <t>79%</t>
+          <t>73%</t>
         </is>
       </c>
       <c r="DZ107" t="inlineStr">
         <is>
-          <t>24%</t>
+          <t>37%</t>
         </is>
       </c>
       <c r="EA107" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="EB107" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="EC107" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="ED107" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="EE107" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="EF107" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="EG107" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.96</t>
         </is>
       </c>
       <c r="EH107" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="EI107" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="EJ107" t="inlineStr"/>
       <c r="EK107" t="inlineStr"/>
-      <c r="EL107" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
-      <c r="EM107" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="EN107" t="inlineStr">
-        <is>
-          <t>3.17</t>
-        </is>
-      </c>
-      <c r="EO107" t="inlineStr">
-        <is>
-          <t>2.83</t>
-        </is>
-      </c>
+      <c r="EL107" t="inlineStr"/>
+      <c r="EM107" t="inlineStr"/>
+      <c r="EN107" t="inlineStr"/>
+      <c r="EO107" t="inlineStr"/>
       <c r="EP107" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.26</t>
         </is>
       </c>
     </row>
@@ -51555,22 +51539,22 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Brentford</t>
+          <t>Aston Villa</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Newcastle United</t>
+          <t>AFC Bournemouth</t>
         </is>
       </c>
       <c r="F108" s="2" t="n">
         <v>45970.58333333334</v>
       </c>
       <c r="G108" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I108" t="n">
         <v>4</v>
@@ -51579,52 +51563,52 @@
         <v>6</v>
       </c>
       <c r="K108" t="n">
-        <v>2</v>
+        <v>9</v>
       </c>
       <c r="L108" t="n">
+        <v>15</v>
+      </c>
+      <c r="M108" t="n">
+        <v>2</v>
+      </c>
+      <c r="N108" t="n">
+        <v>2</v>
+      </c>
+      <c r="O108" t="n">
+        <v>0</v>
+      </c>
+      <c r="P108" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q108" t="n">
         <v>8</v>
       </c>
-      <c r="M108" t="n">
-        <v>2</v>
-      </c>
-      <c r="N108" t="n">
-        <v>2</v>
-      </c>
-      <c r="O108" t="n">
-        <v>0</v>
-      </c>
-      <c r="P108" t="n">
-        <v>1</v>
-      </c>
-      <c r="Q108" t="n">
-        <v>7</v>
-      </c>
       <c r="R108" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="S108" t="n">
         <v>8</v>
       </c>
       <c r="T108" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="U108" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="V108" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="W108" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="X108" t="n">
-        <v>13</v>
+        <v>20</v>
       </c>
       <c r="Y108" t="n">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="Z108" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="AA108" t="inlineStr"/>
       <c r="AB108" t="inlineStr"/>
@@ -51632,25 +51616,25 @@
         <v>2</v>
       </c>
       <c r="AD108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE108" t="n">
-        <v>2.85</v>
+        <v>2.3</v>
       </c>
       <c r="AF108" t="n">
         <v>3.3</v>
       </c>
       <c r="AG108" t="n">
-        <v>2.45</v>
+        <v>2.85</v>
       </c>
       <c r="AH108" t="n">
-        <v>1.24</v>
+        <v>1.28</v>
       </c>
       <c r="AI108" t="n">
-        <v>1.82</v>
+        <v>1.87</v>
       </c>
       <c r="AJ108" t="n">
-        <v>2.88</v>
+        <v>3.2</v>
       </c>
       <c r="AK108" t="n">
         <v>1.65</v>
@@ -51659,58 +51643,58 @@
         <v>2.15</v>
       </c>
       <c r="AM108" t="n">
-        <v>1.41</v>
+        <v>1.33</v>
       </c>
       <c r="AN108" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AO108" t="n">
-        <v>2.83</v>
+        <v>2.78</v>
       </c>
       <c r="AP108" t="n">
-        <v>2.1</v>
+        <v>2.17</v>
       </c>
       <c r="AQ108" t="n">
-        <v>1.38</v>
+        <v>1.33</v>
       </c>
       <c r="AR108" t="n">
         <v>2.6</v>
       </c>
       <c r="AS108" t="n">
-        <v>3.02</v>
+        <v>3.1</v>
       </c>
       <c r="AT108" t="n">
-        <v>1.45</v>
+        <v>1.42</v>
       </c>
       <c r="AU108" t="n">
         <v>4</v>
       </c>
       <c r="AV108" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AW108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AY108" t="n">
         <v>0</v>
       </c>
       <c r="AZ108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BB108" t="n">
-        <v>218</v>
+        <v>158</v>
       </c>
       <c r="BC108" t="n">
         <v>0</v>
       </c>
       <c r="BD108" t="n">
-        <v>50</v>
+        <v>60</v>
       </c>
       <c r="BE108" t="n">
         <v>0</v>
@@ -51725,73 +51709,73 @@
         <v>1</v>
       </c>
       <c r="BI108" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BJ108" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BK108" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BL108" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="BM108" t="n">
         <v>4</v>
       </c>
       <c r="BN108" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="BO108" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BP108" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BQ108" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR108" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BS108" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BT108" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="BU108" t="n">
         <v>1</v>
       </c>
       <c r="BV108" t="n">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="BW108" t="n">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="BX108" t="n">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="BY108" t="n">
-        <v>92</v>
+        <v>77</v>
       </c>
       <c r="BZ108" t="n">
-        <v>1.77</v>
+        <v>1.83</v>
       </c>
       <c r="CA108" t="n">
-        <v>0.65</v>
+        <v>1.26</v>
       </c>
       <c r="CB108" t="n">
-        <v>2.42</v>
+        <v>3.09</v>
       </c>
       <c r="CC108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD108" t="n">
         <v>0</v>
       </c>
       <c r="CE108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF108" t="n">
         <v>0</v>
@@ -51830,73 +51814,73 @@
         <v>1</v>
       </c>
       <c r="CR108" t="n">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="CS108" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="CT108" t="n">
         <v>1</v>
       </c>
       <c r="CU108" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="CV108" t="n">
-        <v>12</v>
+        <v>7</v>
       </c>
       <c r="CW108" t="n">
         <v>1</v>
       </c>
       <c r="CX108" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="CY108" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="CZ108" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="DA108" t="n">
-        <v>50</v>
+        <v>70</v>
       </c>
       <c r="DB108" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="DC108" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
       <c r="DD108" t="n">
         <v>2.17</v>
       </c>
       <c r="DE108" t="n">
-        <v>0.5</v>
+        <v>0.83</v>
       </c>
       <c r="DF108" t="n">
         <v>2</v>
       </c>
       <c r="DG108" t="n">
-        <v>0.6</v>
+        <v>1</v>
       </c>
       <c r="DH108" t="n">
-        <v>1.3</v>
+        <v>1.5</v>
       </c>
       <c r="DI108" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DJ108" t="n">
+        <v>30</v>
+      </c>
+      <c r="DK108" t="n">
+        <v>30</v>
+      </c>
+      <c r="DL108" t="n">
         <v>1.2</v>
       </c>
-      <c r="DJ108" t="n">
-        <v>50</v>
-      </c>
-      <c r="DK108" t="n">
-        <v>50</v>
-      </c>
-      <c r="DL108" t="n">
-        <v>1.24</v>
-      </c>
       <c r="DM108" t="n">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="DN108" t="n">
-        <v>2.65</v>
+        <v>2.62</v>
       </c>
       <c r="DO108" t="n">
         <v>12</v>
@@ -51920,78 +51904,94 @@
         <v>0</v>
       </c>
       <c r="DV108" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW108" t="n">
-        <v>12.74</v>
+        <v>11.54</v>
       </c>
       <c r="DX108" t="n">
-        <v>4.53</v>
+        <v>5.01</v>
       </c>
       <c r="DY108" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>79%</t>
         </is>
       </c>
       <c r="DZ108" t="inlineStr">
         <is>
-          <t>37%</t>
+          <t>24%</t>
         </is>
       </c>
       <c r="EA108" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="EB108" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="EC108" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="ED108" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="EE108" t="inlineStr">
         <is>
-          <t>3.45</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="EF108" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="EG108" t="inlineStr">
         <is>
-          <t>2.96</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="EH108" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="EI108" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="EJ108" t="inlineStr"/>
       <c r="EK108" t="inlineStr"/>
-      <c r="EL108" t="inlineStr"/>
-      <c r="EM108" t="inlineStr"/>
-      <c r="EN108" t="inlineStr"/>
-      <c r="EO108" t="inlineStr"/>
+      <c r="EL108" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EM108" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EN108" t="inlineStr">
+        <is>
+          <t>3.17</t>
+        </is>
+      </c>
+      <c r="EO108" t="inlineStr">
+        <is>
+          <t>2.83</t>
+        </is>
+      </c>
       <c r="EP108" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.28</t>
         </is>
       </c>
     </row>
@@ -53927,12 +53927,12 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Wolverhampton Wanderers</t>
+          <t>Liverpool</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Crystal Palace</t>
+          <t>Nottingham Forest</t>
         </is>
       </c>
       <c r="F113" s="2" t="n">
@@ -53942,134 +53942,134 @@
         <v>0</v>
       </c>
       <c r="H113" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I113" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="J113" t="n">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="K113" t="n">
+        <v>6</v>
+      </c>
+      <c r="L113" t="n">
+        <v>14</v>
+      </c>
+      <c r="M113" t="n">
+        <v>2</v>
+      </c>
+      <c r="N113" t="n">
+        <v>0</v>
+      </c>
+      <c r="O113" t="n">
+        <v>0</v>
+      </c>
+      <c r="P113" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q113" t="n">
         <v>4</v>
       </c>
-      <c r="L113" t="n">
-        <v>5</v>
-      </c>
-      <c r="M113" t="n">
-        <v>2</v>
-      </c>
-      <c r="N113" t="n">
+      <c r="R113" t="n">
+        <v>7</v>
+      </c>
+      <c r="S113" t="n">
+        <v>17</v>
+      </c>
+      <c r="T113" t="n">
+        <v>8</v>
+      </c>
+      <c r="U113" t="n">
+        <v>21</v>
+      </c>
+      <c r="V113" t="n">
+        <v>15</v>
+      </c>
+      <c r="W113" t="n">
+        <v>11</v>
+      </c>
+      <c r="X113" t="n">
+        <v>8</v>
+      </c>
+      <c r="Y113" t="n">
+        <v>75</v>
+      </c>
+      <c r="Z113" t="n">
+        <v>25</v>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>Anfield</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>Anfield Road, Liverpool</t>
+        </is>
+      </c>
+      <c r="AC113" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD113" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AF113" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="AG113" t="n">
+        <v>7</v>
+      </c>
+      <c r="AH113" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="AI113" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="AJ113" t="n">
+        <v>2.24</v>
+      </c>
+      <c r="AK113" t="n">
+        <v>1.77</v>
+      </c>
+      <c r="AL113" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM113" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AN113" t="n">
+        <v>1.56</v>
+      </c>
+      <c r="AO113" t="n">
+        <v>3.07</v>
+      </c>
+      <c r="AP113" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="AQ113" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AR113" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AS113" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AT113" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="AU113" t="n">
         <v>3</v>
       </c>
-      <c r="O113" t="n">
-        <v>0</v>
-      </c>
-      <c r="P113" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q113" t="n">
-        <v>1</v>
-      </c>
-      <c r="R113" t="n">
-        <v>4</v>
-      </c>
-      <c r="S113" t="n">
-        <v>7</v>
-      </c>
-      <c r="T113" t="n">
-        <v>6</v>
-      </c>
-      <c r="U113" t="n">
-        <v>8</v>
-      </c>
-      <c r="V113" t="n">
-        <v>10</v>
-      </c>
-      <c r="W113" t="n">
-        <v>13</v>
-      </c>
-      <c r="X113" t="n">
-        <v>9</v>
-      </c>
-      <c r="Y113" t="n">
-        <v>48</v>
-      </c>
-      <c r="Z113" t="n">
-        <v>52</v>
-      </c>
-      <c r="AA113" t="inlineStr">
-        <is>
-          <t>Molineux Stadium</t>
-        </is>
-      </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>Waterloo Road, Wolverhampton, West Midlands</t>
-        </is>
-      </c>
-      <c r="AC113" t="n">
-        <v>2</v>
-      </c>
-      <c r="AD113" t="n">
-        <v>3</v>
-      </c>
-      <c r="AE113" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="AF113" t="n">
-        <v>3.35</v>
-      </c>
-      <c r="AG113" t="n">
-        <v>1.78</v>
-      </c>
-      <c r="AH113" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AI113" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AJ113" t="n">
-        <v>3.34</v>
-      </c>
-      <c r="AK113" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AL113" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AM113" t="n">
-        <v>1.59</v>
-      </c>
-      <c r="AN113" t="n">
-        <v>2.28</v>
-      </c>
-      <c r="AO113" t="n">
-        <v>2.33</v>
-      </c>
-      <c r="AP113" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AQ113" t="n">
-        <v>1.43</v>
-      </c>
-      <c r="AR113" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="AS113" t="n">
-        <v>2.81</v>
-      </c>
-      <c r="AT113" t="n">
-        <v>1.39</v>
-      </c>
-      <c r="AU113" t="n">
-        <v>2</v>
-      </c>
       <c r="AV113" t="n">
         <v>0</v>
       </c>
       <c r="AW113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AX113" t="n">
         <v>0</v>
@@ -54081,16 +54081,16 @@
         <v>2</v>
       </c>
       <c r="BA113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB113" t="n">
-        <v>143</v>
+        <v>211</v>
       </c>
       <c r="BC113" t="n">
         <v>0</v>
       </c>
       <c r="BD113" t="n">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="BE113" t="n">
         <v>0</v>
@@ -54105,178 +54105,178 @@
         <v>1</v>
       </c>
       <c r="BI113" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="BJ113" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BK113" t="n">
         <v>1</v>
       </c>
       <c r="BL113" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BM113" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="BN113" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="BO113" t="n">
         <v>0</v>
       </c>
       <c r="BP113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BQ113" t="n">
         <v>2</v>
       </c>
       <c r="BR113" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BS113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT113" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BU113" t="n">
         <v>1</v>
       </c>
       <c r="BV113" t="n">
-        <v>33</v>
+        <v>95</v>
       </c>
       <c r="BW113" t="n">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="BX113" t="n">
-        <v>65</v>
+        <v>106</v>
       </c>
       <c r="BY113" t="n">
-        <v>78</v>
+        <v>60</v>
       </c>
       <c r="BZ113" t="n">
+        <v>2.28</v>
+      </c>
+      <c r="CA113" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="CB113" t="n">
+        <v>4.01</v>
+      </c>
+      <c r="CC113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI113" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ113" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM113" t="n">
+        <v>2</v>
+      </c>
+      <c r="CN113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP113" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ113" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR113" t="n">
+        <v>25</v>
+      </c>
+      <c r="CS113" t="n">
+        <v>17</v>
+      </c>
+      <c r="CT113" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU113" t="n">
+        <v>8</v>
+      </c>
+      <c r="CV113" t="n">
+        <v>11</v>
+      </c>
+      <c r="CW113" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX113" t="n">
+        <v>2</v>
+      </c>
+      <c r="CY113" t="n">
+        <v>14</v>
+      </c>
+      <c r="CZ113" t="n">
+        <v>40</v>
+      </c>
+      <c r="DA113" t="n">
+        <v>90</v>
+      </c>
+      <c r="DB113" t="n">
+        <v>30</v>
+      </c>
+      <c r="DC113" t="n">
+        <v>80</v>
+      </c>
+      <c r="DD113" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE113" t="n">
+        <v>0.83</v>
+      </c>
+      <c r="DF113" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="DG113" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="DH113" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="DI113" t="n">
         <v>0.82</v>
       </c>
-      <c r="CA113" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="CB113" t="n">
-        <v>2.07</v>
-      </c>
-      <c r="CC113" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD113" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE113" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF113" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG113" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH113" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI113" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ113" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK113" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL113" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM113" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN113" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO113" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP113" t="n">
-        <v>1</v>
-      </c>
-      <c r="CQ113" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR113" t="n">
-        <v>19</v>
-      </c>
-      <c r="CS113" t="n">
-        <v>16</v>
-      </c>
-      <c r="CT113" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU113" t="n">
-        <v>9</v>
-      </c>
-      <c r="CV113" t="n">
-        <v>13</v>
-      </c>
-      <c r="CW113" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX113" t="n">
-        <v>7</v>
-      </c>
-      <c r="CY113" t="n">
-        <v>6</v>
-      </c>
-      <c r="CZ113" t="n">
-        <v>70</v>
-      </c>
-      <c r="DA113" t="n">
-        <v>80</v>
-      </c>
-      <c r="DB113" t="n">
-        <v>40</v>
-      </c>
-      <c r="DC113" t="n">
-        <v>90</v>
-      </c>
-      <c r="DD113" t="n">
-        <v>0.17</v>
-      </c>
-      <c r="DE113" t="n">
-        <v>1.67</v>
-      </c>
-      <c r="DF113" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="DG113" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="DH113" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="DI113" t="n">
-        <v>1.55</v>
-      </c>
       <c r="DJ113" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="DK113" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="DL113" t="n">
-        <v>1.39</v>
+        <v>1.66</v>
       </c>
       <c r="DM113" t="n">
-        <v>1.26</v>
+        <v>1.15</v>
       </c>
       <c r="DN113" t="n">
-        <v>2.65</v>
+        <v>2.81</v>
       </c>
       <c r="DO113" t="n">
         <v>12</v>
@@ -54288,7 +54288,7 @@
         <v>1</v>
       </c>
       <c r="DR113" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS113" t="b">
         <v>0</v>
@@ -54303,85 +54303,73 @@
         <v>0</v>
       </c>
       <c r="DW113" t="n">
-        <v>3.93</v>
+        <v>5.38</v>
       </c>
       <c r="DX113" t="n">
-        <v>5.71</v>
+        <v>4.78</v>
       </c>
       <c r="DY113" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>91%</t>
         </is>
       </c>
       <c r="DZ113" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>96%</t>
         </is>
       </c>
       <c r="EA113" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="EB113" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>2.56</t>
         </is>
       </c>
       <c r="EC113" t="inlineStr">
         <is>
-          <t>2.18</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="ED113" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>2.47</t>
         </is>
       </c>
       <c r="EE113" t="inlineStr">
         <is>
-          <t>3.81</t>
+          <t>4.78</t>
         </is>
       </c>
       <c r="EF113" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>7.15</t>
         </is>
       </c>
       <c r="EG113" t="inlineStr">
         <is>
-          <t>4.55</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="EH113" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="EI113" t="inlineStr">
         <is>
-          <t>1.87</t>
-        </is>
-      </c>
-      <c r="EJ113" t="inlineStr">
-        <is>
-          <t>1.69</t>
-        </is>
-      </c>
-      <c r="EK113" t="inlineStr">
-        <is>
-          <t>2.17</t>
-        </is>
-      </c>
+          <t>1.79</t>
+        </is>
+      </c>
+      <c r="EJ113" t="inlineStr"/>
+      <c r="EK113" t="inlineStr"/>
       <c r="EL113" t="inlineStr"/>
       <c r="EM113" t="inlineStr"/>
       <c r="EN113" t="inlineStr"/>
       <c r="EO113" t="inlineStr"/>
-      <c r="EP113" t="inlineStr">
-        <is>
-          <t>1.31</t>
-        </is>
-      </c>
+      <c r="EP113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -54875,37 +54863,37 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Fulham</t>
+          <t>Wolverhampton Wanderers</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Sunderland</t>
+          <t>Crystal Palace</t>
         </is>
       </c>
       <c r="F115" s="2" t="n">
         <v>45983.625</v>
       </c>
       <c r="G115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J115" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="K115" t="n">
         <v>4</v>
       </c>
       <c r="L115" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="M115" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N115" t="n">
         <v>3</v>
@@ -54917,101 +54905,101 @@
         <v>0</v>
       </c>
       <c r="Q115" t="n">
+        <v>1</v>
+      </c>
+      <c r="R115" t="n">
+        <v>4</v>
+      </c>
+      <c r="S115" t="n">
+        <v>7</v>
+      </c>
+      <c r="T115" t="n">
         <v>6</v>
       </c>
-      <c r="R115" t="n">
-        <v>2</v>
-      </c>
-      <c r="S115" t="n">
-        <v>18</v>
-      </c>
-      <c r="T115" t="n">
-        <v>2</v>
-      </c>
       <c r="U115" t="n">
-        <v>24</v>
+        <v>8</v>
       </c>
       <c r="V115" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="W115" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="X115" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="Y115" t="n">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="Z115" t="n">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>Craven Cottage</t>
+          <t>Molineux Stadium</t>
         </is>
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>Stevenage Road, London</t>
+          <t>Waterloo Road, Wolverhampton, West Midlands</t>
         </is>
       </c>
       <c r="AC115" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD115" t="n">
         <v>3</v>
       </c>
       <c r="AE115" t="n">
-        <v>1.94</v>
+        <v>4.2</v>
       </c>
       <c r="AF115" t="n">
-        <v>3.36</v>
+        <v>3.35</v>
       </c>
       <c r="AG115" t="n">
-        <v>3.5</v>
+        <v>1.78</v>
       </c>
       <c r="AH115" t="n">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="AI115" t="n">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="AJ115" t="n">
-        <v>3.7</v>
+        <v>3.34</v>
       </c>
       <c r="AK115" t="n">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="AL115" t="n">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AM115" t="n">
-        <v>1.35</v>
+        <v>1.59</v>
       </c>
       <c r="AN115" t="n">
-        <v>1.91</v>
+        <v>2.28</v>
       </c>
       <c r="AO115" t="n">
-        <v>2.62</v>
+        <v>2.33</v>
       </c>
       <c r="AP115" t="n">
-        <v>2.05</v>
+        <v>1.83</v>
       </c>
       <c r="AQ115" t="n">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="AR115" t="n">
-        <v>2.9</v>
+        <v>2.8</v>
       </c>
       <c r="AS115" t="n">
-        <v>2.6</v>
+        <v>2.81</v>
       </c>
       <c r="AT115" t="n">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="AU115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AV115" t="n">
         <v>0</v>
@@ -55020,25 +55008,25 @@
         <v>0</v>
       </c>
       <c r="AX115" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ115" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BA115" t="n">
         <v>0</v>
       </c>
       <c r="BB115" t="n">
-        <v>162</v>
+        <v>143</v>
       </c>
       <c r="BC115" t="n">
         <v>0</v>
       </c>
       <c r="BD115" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="BE115" t="n">
         <v>0</v>
@@ -55053,64 +55041,64 @@
         <v>1</v>
       </c>
       <c r="BI115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BJ115" t="n">
         <v>3</v>
       </c>
-      <c r="BJ115" t="n">
-        <v>2</v>
-      </c>
       <c r="BK115" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL115" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM115" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN115" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO115" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP115" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ115" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR115" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS115" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT115" t="n">
         <v>4</v>
       </c>
-      <c r="BL115" t="n">
-        <v>2</v>
-      </c>
-      <c r="BM115" t="n">
-        <v>5</v>
-      </c>
-      <c r="BN115" t="n">
-        <v>6</v>
-      </c>
-      <c r="BO115" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP115" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ115" t="n">
-        <v>3</v>
-      </c>
-      <c r="BR115" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS115" t="n">
-        <v>1</v>
-      </c>
-      <c r="BT115" t="n">
-        <v>5</v>
-      </c>
       <c r="BU115" t="n">
         <v>1</v>
       </c>
       <c r="BV115" t="n">
-        <v>68</v>
+        <v>33</v>
       </c>
       <c r="BW115" t="n">
-        <v>40</v>
+        <v>47</v>
       </c>
       <c r="BX115" t="n">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="BY115" t="n">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="BZ115" t="n">
-        <v>2.41</v>
+        <v>0.82</v>
       </c>
       <c r="CA115" t="n">
-        <v>0.6899999999999999</v>
+        <v>1.25</v>
       </c>
       <c r="CB115" t="n">
-        <v>3.1</v>
+        <v>2.07</v>
       </c>
       <c r="CC115" t="n">
         <v>0</v>
@@ -55152,25 +55140,25 @@
         <v>0</v>
       </c>
       <c r="CP115" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CQ115" t="n">
         <v>1</v>
       </c>
       <c r="CR115" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="CS115" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="CT115" t="n">
         <v>1</v>
       </c>
       <c r="CU115" t="n">
+        <v>9</v>
+      </c>
+      <c r="CV115" t="n">
         <v>13</v>
-      </c>
-      <c r="CV115" t="n">
-        <v>5</v>
       </c>
       <c r="CW115" t="n">
         <v>1</v>
@@ -55179,52 +55167,52 @@
         <v>7</v>
       </c>
       <c r="CY115" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="CZ115" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="DA115" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="DB115" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="DC115" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="DD115" t="n">
-        <v>2.17</v>
+        <v>0.17</v>
       </c>
       <c r="DE115" t="n">
-        <v>1.17</v>
+        <v>1.67</v>
       </c>
       <c r="DF115" t="n">
-        <v>2</v>
+        <v>0.2</v>
       </c>
       <c r="DG115" t="n">
         <v>1.4</v>
       </c>
       <c r="DH115" t="n">
-        <v>1</v>
+        <v>0.18</v>
       </c>
       <c r="DI115" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="DJ115" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="DK115" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="DL115" t="n">
-        <v>1.32</v>
+        <v>1.39</v>
       </c>
       <c r="DM115" t="n">
-        <v>0.99</v>
+        <v>1.26</v>
       </c>
       <c r="DN115" t="n">
-        <v>2.31</v>
+        <v>2.65</v>
       </c>
       <c r="DO115" t="n">
         <v>12</v>
@@ -55233,7 +55221,7 @@
         <v>1</v>
       </c>
       <c r="DQ115" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR115" t="b">
         <v>0</v>
@@ -55251,14 +55239,14 @@
         <v>0</v>
       </c>
       <c r="DW115" t="n">
-        <v>6.97</v>
+        <v>3.93</v>
       </c>
       <c r="DX115" t="n">
-        <v>5.43</v>
+        <v>5.71</v>
       </c>
       <c r="DY115" t="inlineStr">
         <is>
-          <t>84%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="DZ115" t="inlineStr">
@@ -55268,78 +55256,66 @@
       </c>
       <c r="EA115" t="inlineStr">
         <is>
-          <t>2.13</t>
-        </is>
-      </c>
-      <c r="EB115" t="inlineStr"/>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EB115" t="inlineStr">
+        <is>
+          <t>3.44</t>
+        </is>
+      </c>
       <c r="EC115" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>2.18</t>
         </is>
       </c>
       <c r="ED115" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="EE115" t="inlineStr">
         <is>
-          <t>3.38</t>
+          <t>3.81</t>
         </is>
       </c>
       <c r="EF115" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="EG115" t="inlineStr">
         <is>
-          <t>2.07</t>
+          <t>4.55</t>
         </is>
       </c>
       <c r="EH115" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="EI115" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="EJ115" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="EK115" t="inlineStr">
         <is>
-          <t>2.46</t>
-        </is>
-      </c>
-      <c r="EL115" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="EM115" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="EN115" t="inlineStr">
-        <is>
-          <t>2.83</t>
-        </is>
-      </c>
-      <c r="EO115" t="inlineStr">
-        <is>
-          <t>3.18</t>
-        </is>
-      </c>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="EL115" t="inlineStr"/>
+      <c r="EM115" t="inlineStr"/>
+      <c r="EN115" t="inlineStr"/>
+      <c r="EO115" t="inlineStr"/>
       <c r="EP115" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.31</t>
         </is>
       </c>
     </row>
@@ -55839,170 +55815,170 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Liverpool</t>
+          <t>Fulham</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Nottingham Forest</t>
+          <t>Sunderland</t>
         </is>
       </c>
       <c r="F117" s="2" t="n">
         <v>45983.625</v>
       </c>
       <c r="G117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H117" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" t="n">
+        <v>1</v>
+      </c>
+      <c r="J117" t="n">
+        <v>7</v>
+      </c>
+      <c r="K117" t="n">
+        <v>4</v>
+      </c>
+      <c r="L117" t="n">
+        <v>11</v>
+      </c>
+      <c r="M117" t="n">
         <v>3</v>
       </c>
-      <c r="I117" t="n">
+      <c r="N117" t="n">
         <v>3</v>
       </c>
-      <c r="J117" t="n">
-        <v>8</v>
-      </c>
-      <c r="K117" t="n">
+      <c r="O117" t="n">
+        <v>0</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q117" t="n">
         <v>6</v>
       </c>
-      <c r="L117" t="n">
-        <v>14</v>
-      </c>
-      <c r="M117" t="n">
-        <v>2</v>
-      </c>
-      <c r="N117" t="n">
-        <v>0</v>
-      </c>
-      <c r="O117" t="n">
-        <v>0</v>
-      </c>
-      <c r="P117" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q117" t="n">
+      <c r="R117" t="n">
+        <v>2</v>
+      </c>
+      <c r="S117" t="n">
+        <v>18</v>
+      </c>
+      <c r="T117" t="n">
+        <v>2</v>
+      </c>
+      <c r="U117" t="n">
+        <v>24</v>
+      </c>
+      <c r="V117" t="n">
         <v>4</v>
       </c>
-      <c r="R117" t="n">
-        <v>7</v>
-      </c>
-      <c r="S117" t="n">
-        <v>17</v>
-      </c>
-      <c r="T117" t="n">
-        <v>8</v>
-      </c>
-      <c r="U117" t="n">
-        <v>21</v>
-      </c>
-      <c r="V117" t="n">
-        <v>15</v>
-      </c>
       <c r="W117" t="n">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="X117" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="Y117" t="n">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="Z117" t="n">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>Anfield</t>
+          <t>Craven Cottage</t>
         </is>
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>Anfield Road, Liverpool</t>
+          <t>Stevenage Road, London</t>
         </is>
       </c>
       <c r="AC117" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD117" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AE117" t="n">
-        <v>1.36</v>
+        <v>1.94</v>
       </c>
       <c r="AF117" t="n">
-        <v>4.6</v>
+        <v>3.36</v>
       </c>
       <c r="AG117" t="n">
-        <v>7</v>
+        <v>3.5</v>
       </c>
       <c r="AH117" t="n">
-        <v>1.12</v>
+        <v>1.34</v>
       </c>
       <c r="AI117" t="n">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="AJ117" t="n">
-        <v>2.24</v>
+        <v>3.7</v>
       </c>
       <c r="AK117" t="n">
-        <v>1.77</v>
+        <v>1.8</v>
       </c>
       <c r="AL117" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="AP117" t="n">
         <v>2.05</v>
       </c>
-      <c r="AM117" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="AN117" t="n">
-        <v>1.56</v>
-      </c>
-      <c r="AO117" t="n">
-        <v>3.07</v>
-      </c>
-      <c r="AP117" t="n">
-        <v>2.32</v>
-      </c>
       <c r="AQ117" t="n">
-        <v>1.25</v>
+        <v>1.45</v>
       </c>
       <c r="AR117" t="n">
-        <v>2.2</v>
+        <v>2.9</v>
       </c>
       <c r="AS117" t="n">
-        <v>3.7</v>
+        <v>2.6</v>
       </c>
       <c r="AT117" t="n">
-        <v>1.59</v>
+        <v>1.37</v>
       </c>
       <c r="AU117" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AV117" t="n">
         <v>0</v>
       </c>
       <c r="AW117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AX117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY117" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ117" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA117" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB117" t="n">
-        <v>211</v>
+        <v>162</v>
       </c>
       <c r="BC117" t="n">
         <v>0</v>
       </c>
       <c r="BD117" t="n">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="BE117" t="n">
         <v>0</v>
@@ -56017,19 +55993,19 @@
         <v>1</v>
       </c>
       <c r="BI117" t="n">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="BJ117" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BK117" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="BL117" t="n">
+        <v>2</v>
+      </c>
+      <c r="BM117" t="n">
         <v>5</v>
-      </c>
-      <c r="BM117" t="n">
-        <v>8</v>
       </c>
       <c r="BN117" t="n">
         <v>6</v>
@@ -56038,43 +56014,43 @@
         <v>0</v>
       </c>
       <c r="BP117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ117" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BR117" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BS117" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BT117" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BU117" t="n">
         <v>1</v>
       </c>
       <c r="BV117" t="n">
-        <v>95</v>
+        <v>68</v>
       </c>
       <c r="BW117" t="n">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BX117" t="n">
-        <v>106</v>
+        <v>73</v>
       </c>
       <c r="BY117" t="n">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="BZ117" t="n">
-        <v>2.28</v>
+        <v>2.41</v>
       </c>
       <c r="CA117" t="n">
-        <v>1.73</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="CB117" t="n">
-        <v>4.01</v>
+        <v>3.1</v>
       </c>
       <c r="CC117" t="n">
         <v>0</v>
@@ -56107,7 +56083,7 @@
         <v>0</v>
       </c>
       <c r="CM117" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CN117" t="n">
         <v>0</v>
@@ -56122,7 +56098,7 @@
         <v>1</v>
       </c>
       <c r="CR117" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="CS117" t="n">
         <v>17</v>
@@ -56131,64 +56107,64 @@
         <v>1</v>
       </c>
       <c r="CU117" t="n">
-        <v>8</v>
+        <v>13</v>
       </c>
       <c r="CV117" t="n">
+        <v>5</v>
+      </c>
+      <c r="CW117" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX117" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY117" t="n">
         <v>11</v>
       </c>
-      <c r="CW117" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX117" t="n">
-        <v>2</v>
-      </c>
-      <c r="CY117" t="n">
-        <v>14</v>
-      </c>
       <c r="CZ117" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="DA117" t="n">
-        <v>90</v>
+        <v>60</v>
       </c>
       <c r="DB117" t="n">
         <v>30</v>
       </c>
       <c r="DC117" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="DD117" t="n">
-        <v>2</v>
+        <v>2.17</v>
       </c>
       <c r="DE117" t="n">
-        <v>0.83</v>
+        <v>1.17</v>
       </c>
       <c r="DF117" t="n">
-        <v>2.4</v>
+        <v>2</v>
       </c>
       <c r="DG117" t="n">
-        <v>0.4</v>
+        <v>1.4</v>
       </c>
       <c r="DH117" t="n">
-        <v>1.64</v>
+        <v>1</v>
       </c>
       <c r="DI117" t="n">
-        <v>0.82</v>
+        <v>1.73</v>
       </c>
       <c r="DJ117" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="DK117" t="n">
-        <v>10</v>
+        <v>40</v>
       </c>
       <c r="DL117" t="n">
-        <v>1.66</v>
+        <v>1.32</v>
       </c>
       <c r="DM117" t="n">
-        <v>1.15</v>
+        <v>0.99</v>
       </c>
       <c r="DN117" t="n">
-        <v>2.81</v>
+        <v>2.31</v>
       </c>
       <c r="DO117" t="n">
         <v>12</v>
@@ -56197,10 +56173,10 @@
         <v>1</v>
       </c>
       <c r="DQ117" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR117" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS117" t="b">
         <v>0</v>
@@ -56215,73 +56191,97 @@
         <v>0</v>
       </c>
       <c r="DW117" t="n">
-        <v>5.38</v>
+        <v>6.97</v>
       </c>
       <c r="DX117" t="n">
-        <v>4.78</v>
+        <v>5.43</v>
       </c>
       <c r="DY117" t="inlineStr">
         <is>
-          <t>91%</t>
+          <t>84%</t>
         </is>
       </c>
       <c r="DZ117" t="inlineStr">
         <is>
-          <t>96%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EA117" t="inlineStr">
         <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="EB117" t="inlineStr">
-        <is>
-          <t>2.56</t>
-        </is>
-      </c>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="EB117" t="inlineStr"/>
       <c r="EC117" t="inlineStr">
         <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="ED117" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="EE117" t="inlineStr">
+        <is>
+          <t>3.38</t>
+        </is>
+      </c>
+      <c r="EF117" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="EG117" t="inlineStr">
+        <is>
+          <t>2.07</t>
+        </is>
+      </c>
+      <c r="EH117" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EI117" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="EJ117" t="inlineStr">
+        <is>
           <t>1.53</t>
         </is>
       </c>
-      <c r="ED117" t="inlineStr">
-        <is>
-          <t>2.47</t>
-        </is>
-      </c>
-      <c r="EE117" t="inlineStr">
-        <is>
-          <t>4.78</t>
-        </is>
-      </c>
-      <c r="EF117" t="inlineStr">
-        <is>
-          <t>7.15</t>
-        </is>
-      </c>
-      <c r="EG117" t="inlineStr">
-        <is>
-          <t>1.46</t>
-        </is>
-      </c>
-      <c r="EH117" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="EI117" t="inlineStr">
-        <is>
-          <t>1.79</t>
-        </is>
-      </c>
-      <c r="EJ117" t="inlineStr"/>
-      <c r="EK117" t="inlineStr"/>
-      <c r="EL117" t="inlineStr"/>
-      <c r="EM117" t="inlineStr"/>
-      <c r="EN117" t="inlineStr"/>
-      <c r="EO117" t="inlineStr"/>
-      <c r="EP117" t="inlineStr"/>
+      <c r="EK117" t="inlineStr">
+        <is>
+          <t>2.46</t>
+        </is>
+      </c>
+      <c r="EL117" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EM117" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="EN117" t="inlineStr">
+        <is>
+          <t>2.83</t>
+        </is>
+      </c>
+      <c r="EO117" t="inlineStr">
+        <is>
+          <t>3.18</t>
+        </is>
+      </c>
+      <c r="EP117" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -57699,6 +57699,494 @@
         </is>
       </c>
     </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>England_Premier_League_2025-2026</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>12</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>Manchester United</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>Everton</t>
+        </is>
+      </c>
+      <c r="F121" s="2" t="n">
+        <v>45985.83333333334</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" t="n">
+        <v>1</v>
+      </c>
+      <c r="I121" t="n">
+        <v>1</v>
+      </c>
+      <c r="J121" t="n">
+        <v>9</v>
+      </c>
+      <c r="K121" t="n">
+        <v>1</v>
+      </c>
+      <c r="L121" t="n">
+        <v>10</v>
+      </c>
+      <c r="M121" t="n">
+        <v>2</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0</v>
+      </c>
+      <c r="P121" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>6</v>
+      </c>
+      <c r="R121" t="n">
+        <v>1</v>
+      </c>
+      <c r="S121" t="n">
+        <v>19</v>
+      </c>
+      <c r="T121" t="n">
+        <v>2</v>
+      </c>
+      <c r="U121" t="n">
+        <v>25</v>
+      </c>
+      <c r="V121" t="n">
+        <v>3</v>
+      </c>
+      <c r="W121" t="n">
+        <v>12</v>
+      </c>
+      <c r="X121" t="n">
+        <v>9</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>70</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>30</v>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>Old Trafford</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>Sir Matt Busby Way, Manchester</t>
+        </is>
+      </c>
+      <c r="AC121" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>4.22</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>144</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>60</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>6</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>3</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>7</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>2</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>1</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>91</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>30</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>150</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>95</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>19</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>18</v>
+      </c>
+      <c r="CT121" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU121" t="n">
+        <v>11</v>
+      </c>
+      <c r="CV121" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW121" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX121" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY121" t="n">
+        <v>20</v>
+      </c>
+      <c r="CZ121" t="n">
+        <v>50</v>
+      </c>
+      <c r="DA121" t="n">
+        <v>80</v>
+      </c>
+      <c r="DB121" t="n">
+        <v>50</v>
+      </c>
+      <c r="DC121" t="n">
+        <v>80</v>
+      </c>
+      <c r="DD121" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE121" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="DF121" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="DG121" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="DH121" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="DI121" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="DJ121" t="n">
+        <v>50</v>
+      </c>
+      <c r="DK121" t="n">
+        <v>20</v>
+      </c>
+      <c r="DL121" t="n">
+        <v>1.92</v>
+      </c>
+      <c r="DM121" t="n">
+        <v>0.92</v>
+      </c>
+      <c r="DN121" t="n">
+        <v>2.84</v>
+      </c>
+      <c r="DO121" t="n">
+        <v>12</v>
+      </c>
+      <c r="DP121" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ121" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR121" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS121" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT121" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU121" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV121" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW121" t="n">
+        <v>7.79</v>
+      </c>
+      <c r="DX121" t="n">
+        <v>5.86</v>
+      </c>
+      <c r="DY121" t="inlineStr">
+        <is>
+          <t>74%</t>
+        </is>
+      </c>
+      <c r="DZ121" t="inlineStr">
+        <is>
+          <t>97%</t>
+        </is>
+      </c>
+      <c r="EA121" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="EB121" t="inlineStr">
+        <is>
+          <t>3.07</t>
+        </is>
+      </c>
+      <c r="EC121" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="ED121" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="EE121" t="inlineStr">
+        <is>
+          <t>3.88</t>
+        </is>
+      </c>
+      <c r="EF121" t="inlineStr">
+        <is>
+          <t>4.09</t>
+        </is>
+      </c>
+      <c r="EG121" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
+      </c>
+      <c r="EH121" t="inlineStr">
+        <is>
+          <t>2.16</t>
+        </is>
+      </c>
+      <c r="EI121" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="EJ121" t="inlineStr">
+        <is>
+          <t>1.51</t>
+        </is>
+      </c>
+      <c r="EK121" t="inlineStr">
+        <is>
+          <t>2.53</t>
+        </is>
+      </c>
+      <c r="EL121" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="EM121" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="EN121" t="inlineStr">
+        <is>
+          <t>3.32</t>
+        </is>
+      </c>
+      <c r="EO121" t="inlineStr">
+        <is>
+          <t>2.71</t>
+        </is>
+      </c>
+      <c r="EP121" t="inlineStr">
+        <is>
+          <t>1.27</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">

--- a/data/matches/leagues/England_Premier_League_2025-2026.xlsx
+++ b/data/matches/leagues/England_Premier_League_2025-2026.xlsx
@@ -97368,7 +97368,7 @@
         <v>0</v>
       </c>
       <c r="BF205" t="n">
-        <v>-1</v>
+        <v>26990</v>
       </c>
       <c r="BG205" t="n">
         <v>2</v>

--- a/data/matches/leagues/England_Premier_League_2025-2026.xlsx
+++ b/data/matches/leagues/England_Premier_League_2025-2026.xlsx
@@ -104452,7 +104452,7 @@
         <v>0</v>
       </c>
       <c r="BF220" t="n">
-        <v>-1</v>
+        <v>42770</v>
       </c>
       <c r="BG220" t="n">
         <v>2</v>
